--- a/salidas/empresas/GM.xlsx
+++ b/salidas/empresas/GM.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EPS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="EPS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Info" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,13 +23,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,12 +51,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -435,58 +447,58 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>precio_ajustado</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>precio_cierre</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>volumen</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pe</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>acciones_circulacion</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>market_cap</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>rotacion</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>40512</v>
       </c>
       <c r="B2" t="n">
-        <v>25.33570098876953</v>
+        <v>25.33570289611816</v>
       </c>
       <c r="C2" t="n">
         <v>34.20000076293945</v>
@@ -501,11 +513,11 @@
       <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>40543</v>
       </c>
       <c r="B3" t="n">
-        <v>27.30625534057617</v>
+        <v>27.30625152587891</v>
       </c>
       <c r="C3" t="n">
         <v>36.86000061035156</v>
@@ -520,11 +532,11 @@
       <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>40574</v>
       </c>
       <c r="B4" t="n">
-        <v>27.03215408325195</v>
+        <v>27.03216552734375</v>
       </c>
       <c r="C4" t="n">
         <v>36.4900016784668</v>
@@ -539,11 +551,11 @@
       <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="B5" t="n">
-        <v>24.83936500549316</v>
+        <v>24.83935737609863</v>
       </c>
       <c r="C5" t="n">
         <v>33.52999877929688</v>
@@ -558,11 +570,11 @@
       <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40633</v>
       </c>
       <c r="B6" t="n">
-        <v>22.98733139038086</v>
+        <v>22.98733711242676</v>
       </c>
       <c r="C6" t="n">
         <v>31.03000068664551</v>
@@ -577,11 +589,11 @@
       <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40663</v>
       </c>
       <c r="B7" t="n">
-        <v>23.7725944519043</v>
+        <v>23.77259063720703</v>
       </c>
       <c r="C7" t="n">
         <v>32.09000015258789</v>
@@ -596,11 +608,11 @@
       <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40694</v>
       </c>
       <c r="B8" t="n">
-        <v>23.56516456604004</v>
+        <v>23.56516265869141</v>
       </c>
       <c r="C8" t="n">
         <v>31.80999946594238</v>
@@ -615,11 +627,11 @@
       <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40724</v>
       </c>
       <c r="B9" t="n">
-        <v>22.49099349975586</v>
+        <v>22.49099731445312</v>
       </c>
       <c r="C9" t="n">
         <v>30.36000061035156</v>
@@ -634,11 +646,11 @@
       <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40755</v>
       </c>
       <c r="B10" t="n">
-        <v>20.50562286376953</v>
+        <v>20.50562477111816</v>
       </c>
       <c r="C10" t="n">
         <v>27.68000030517578</v>
@@ -653,11 +665,11 @@
       <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40786</v>
       </c>
       <c r="B11" t="n">
-        <v>17.80166435241699</v>
+        <v>17.80166053771973</v>
       </c>
       <c r="C11" t="n">
         <v>24.03000068664551</v>
@@ -678,11 +690,11 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40816</v>
       </c>
       <c r="B12" t="n">
-        <v>14.94954109191895</v>
+        <v>14.94954872131348</v>
       </c>
       <c r="C12" t="n">
         <v>20.18000030517578</v>
@@ -703,11 +715,11 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>40847</v>
       </c>
       <c r="B13" t="n">
-        <v>19.14993858337402</v>
+        <v>19.14994049072266</v>
       </c>
       <c r="C13" t="n">
         <v>25.85000038146973</v>
@@ -728,11 +740,11 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>40877</v>
       </c>
       <c r="B14" t="n">
-        <v>15.7718448638916</v>
+        <v>15.77184391021729</v>
       </c>
       <c r="C14" t="n">
         <v>21.29000091552734</v>
@@ -753,7 +765,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>40908</v>
       </c>
       <c r="B15" t="n">
@@ -778,11 +790,11 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>40939</v>
       </c>
       <c r="B16" t="n">
-        <v>17.79425621032715</v>
+        <v>17.79425811767578</v>
       </c>
       <c r="C16" t="n">
         <v>24.02000045776367</v>
@@ -803,11 +815,11 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="B17" t="n">
-        <v>19.27588272094727</v>
+        <v>19.27587890625</v>
       </c>
       <c r="C17" t="n">
         <v>26.02000045776367</v>
@@ -832,11 +844,11 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>40999</v>
       </c>
       <c r="B18" t="n">
-        <v>19.00177192687988</v>
+        <v>19.00177764892578</v>
       </c>
       <c r="C18" t="n">
         <v>25.64999961853027</v>
@@ -861,11 +873,11 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41029</v>
       </c>
       <c r="B19" t="n">
-        <v>17.03863143920898</v>
+        <v>17.03862571716309</v>
       </c>
       <c r="C19" t="n">
         <v>23</v>
@@ -890,11 +902,11 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41060</v>
       </c>
       <c r="B20" t="n">
-        <v>16.44598579406738</v>
+        <v>16.44598388671875</v>
       </c>
       <c r="C20" t="n">
         <v>22.20000076293945</v>
@@ -919,11 +931,11 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41090</v>
       </c>
       <c r="B21" t="n">
-        <v>14.60877418518066</v>
+        <v>14.60877323150635</v>
       </c>
       <c r="C21" t="n">
         <v>19.71999931335449</v>
@@ -948,11 +960,11 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41121</v>
       </c>
       <c r="B22" t="n">
-        <v>14.6013650894165</v>
+        <v>14.60136413574219</v>
       </c>
       <c r="C22" t="n">
         <v>19.70999908447266</v>
@@ -977,11 +989,11 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41152</v>
       </c>
       <c r="B23" t="n">
-        <v>15.81628704071045</v>
+        <v>15.8162956237793</v>
       </c>
       <c r="C23" t="n">
         <v>21.35000038146973</v>
@@ -1006,11 +1018,11 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>41182</v>
       </c>
       <c r="B24" t="n">
-        <v>16.85342216491699</v>
+        <v>16.85342788696289</v>
       </c>
       <c r="C24" t="n">
         <v>22.75</v>
@@ -1035,7 +1047,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>41213</v>
       </c>
       <c r="B25" t="n">
@@ -1060,11 +1072,11 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>41243</v>
       </c>
       <c r="B26" t="n">
-        <v>19.17216491699219</v>
+        <v>19.17216300964355</v>
       </c>
       <c r="C26" t="n">
         <v>25.8799991607666</v>
@@ -1085,7 +1097,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>41274</v>
       </c>
       <c r="B27" t="n">
@@ -1110,11 +1122,11 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>41305</v>
       </c>
       <c r="B28" t="n">
-        <v>20.80935668945312</v>
+        <v>20.80934715270996</v>
       </c>
       <c r="C28" t="n">
         <v>28.09000015258789</v>
@@ -1135,11 +1147,11 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="B29" t="n">
-        <v>20.11298942565918</v>
+        <v>20.11299324035645</v>
       </c>
       <c r="C29" t="n">
         <v>27.14999961853027</v>
@@ -1164,11 +1176,11 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>41364</v>
       </c>
       <c r="B30" t="n">
-        <v>20.60934257507324</v>
+        <v>20.60933303833008</v>
       </c>
       <c r="C30" t="n">
         <v>27.81999969482422</v>
@@ -1193,11 +1205,11 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>41394</v>
       </c>
       <c r="B31" t="n">
-        <v>22.84658241271973</v>
+        <v>22.84658050537109</v>
       </c>
       <c r="C31" t="n">
         <v>30.84000015258789</v>
@@ -1222,11 +1234,11 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>41425</v>
       </c>
       <c r="B32" t="n">
-        <v>25.10605621337891</v>
+        <v>25.10604858398438</v>
       </c>
       <c r="C32" t="n">
         <v>33.88999938964844</v>
@@ -1251,11 +1263,11 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>41455</v>
       </c>
       <c r="B33" t="n">
-        <v>24.67638206481934</v>
+        <v>24.6763801574707</v>
       </c>
       <c r="C33" t="n">
         <v>33.31000137329102</v>
@@ -1280,11 +1292,11 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="B34" t="n">
-        <v>26.57285499572754</v>
+        <v>26.57285118103027</v>
       </c>
       <c r="C34" t="n">
         <v>35.86999893188477</v>
@@ -1309,11 +1321,11 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>41517</v>
       </c>
       <c r="B35" t="n">
-        <v>25.24680328369141</v>
+        <v>25.24680709838867</v>
       </c>
       <c r="C35" t="n">
         <v>34.08000183105469</v>
@@ -1338,11 +1350,11 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>41547</v>
       </c>
       <c r="B36" t="n">
-        <v>26.64693450927734</v>
+        <v>26.64694213867188</v>
       </c>
       <c r="C36" t="n">
         <v>35.97000122070312</v>
@@ -1363,11 +1375,11 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>41578</v>
       </c>
       <c r="B37" t="n">
-        <v>27.37292671203613</v>
+        <v>27.3729305267334</v>
       </c>
       <c r="C37" t="n">
         <v>36.95000076293945</v>
@@ -1388,11 +1400,11 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>41608</v>
       </c>
       <c r="B38" t="n">
-        <v>28.69156837463379</v>
+        <v>28.69156265258789</v>
       </c>
       <c r="C38" t="n">
         <v>38.72999954223633</v>
@@ -1413,11 +1425,11 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>41639</v>
       </c>
       <c r="B39" t="n">
-        <v>30.27690887451172</v>
+        <v>30.27689933776855</v>
       </c>
       <c r="C39" t="n">
         <v>40.86999893188477</v>
@@ -1438,11 +1450,11 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>41670</v>
       </c>
       <c r="B40" t="n">
-        <v>26.72842407226562</v>
+        <v>26.72843170166016</v>
       </c>
       <c r="C40" t="n">
         <v>36.08000183105469</v>
@@ -1463,11 +1475,11 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="B41" t="n">
-        <v>26.81733131408691</v>
+        <v>26.81732940673828</v>
       </c>
       <c r="C41" t="n">
         <v>36.20000076293945</v>
@@ -1492,11 +1504,11 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>41729</v>
       </c>
       <c r="B42" t="n">
-        <v>25.72505950927734</v>
+        <v>25.72507095336914</v>
       </c>
       <c r="C42" t="n">
         <v>34.41999816894531</v>
@@ -1521,11 +1533,11 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>41759</v>
       </c>
       <c r="B43" t="n">
-        <v>25.76991081237793</v>
+        <v>25.76991271972656</v>
       </c>
       <c r="C43" t="n">
         <v>34.47999954223633</v>
@@ -1550,11 +1562,11 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>41790</v>
       </c>
       <c r="B44" t="n">
-        <v>25.84465217590332</v>
+        <v>25.84465026855469</v>
       </c>
       <c r="C44" t="n">
         <v>34.58000183105469</v>
@@ -1579,11 +1591,11 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>41820</v>
       </c>
       <c r="B45" t="n">
-        <v>27.35642242431641</v>
+        <v>27.3564281463623</v>
       </c>
       <c r="C45" t="n">
         <v>36.29999923706055</v>
@@ -1608,11 +1620,11 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="B46" t="n">
-        <v>25.48745346069336</v>
+        <v>25.48744773864746</v>
       </c>
       <c r="C46" t="n">
         <v>33.81999969482422</v>
@@ -1637,7 +1649,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>41882</v>
       </c>
       <c r="B47" t="n">
@@ -1666,11 +1678,11 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>41912</v>
       </c>
       <c r="B48" t="n">
-        <v>24.28129768371582</v>
+        <v>24.28129577636719</v>
       </c>
       <c r="C48" t="n">
         <v>31.94000053405762</v>
@@ -1695,11 +1707,11 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>41943</v>
       </c>
       <c r="B49" t="n">
-        <v>23.87077522277832</v>
+        <v>23.87077903747559</v>
       </c>
       <c r="C49" t="n">
         <v>31.39999961853027</v>
@@ -1724,11 +1736,11 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>41973</v>
       </c>
       <c r="B50" t="n">
-        <v>25.41401672363281</v>
+        <v>25.41401290893555</v>
       </c>
       <c r="C50" t="n">
         <v>33.43000030517578</v>
@@ -1753,11 +1765,11 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>42004</v>
       </c>
       <c r="B51" t="n">
-        <v>26.77588272094727</v>
+        <v>26.77587890625</v>
       </c>
       <c r="C51" t="n">
         <v>34.90999984741211</v>
@@ -1782,11 +1794,11 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>42035</v>
       </c>
       <c r="B52" t="n">
-        <v>25.01945877075195</v>
+        <v>25.01945495605469</v>
       </c>
       <c r="C52" t="n">
         <v>32.61999893188477</v>
@@ -1811,11 +1823,11 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>42063</v>
       </c>
       <c r="B53" t="n">
-        <v>28.61668014526367</v>
+        <v>28.61666870117188</v>
       </c>
       <c r="C53" t="n">
         <v>37.31000137329102</v>
@@ -1840,11 +1852,11 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>42094</v>
       </c>
       <c r="B54" t="n">
-        <v>28.99854278564453</v>
+        <v>28.99855422973633</v>
       </c>
       <c r="C54" t="n">
         <v>37.5</v>
@@ -1869,11 +1881,11 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>42124</v>
       </c>
       <c r="B55" t="n">
-        <v>27.11170768737793</v>
+        <v>27.1117057800293</v>
       </c>
       <c r="C55" t="n">
         <v>35.06000137329102</v>
@@ -1898,11 +1910,11 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>42155</v>
       </c>
       <c r="B56" t="n">
-        <v>27.81540870666504</v>
+        <v>27.81540107727051</v>
       </c>
       <c r="C56" t="n">
         <v>35.97000122070312</v>
@@ -1927,11 +1939,11 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>42185</v>
       </c>
       <c r="B57" t="n">
-        <v>26.04084396362305</v>
+        <v>26.04084014892578</v>
       </c>
       <c r="C57" t="n">
         <v>33.33000183105469</v>
@@ -1956,11 +1968,11 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>42216</v>
       </c>
       <c r="B58" t="n">
-        <v>24.61887168884277</v>
+        <v>24.61886978149414</v>
       </c>
       <c r="C58" t="n">
         <v>31.51000022888184</v>
@@ -1985,11 +1997,11 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>42247</v>
       </c>
       <c r="B59" t="n">
-        <v>23.0015697479248</v>
+        <v>23.00157165527344</v>
       </c>
       <c r="C59" t="n">
         <v>29.44000053405762</v>
@@ -2014,11 +2026,11 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>42277</v>
       </c>
       <c r="B60" t="n">
-        <v>23.7433032989502</v>
+        <v>23.74330139160156</v>
       </c>
       <c r="C60" t="n">
         <v>30.02000045776367</v>
@@ -2043,7 +2055,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>42308</v>
       </c>
       <c r="B61" t="n">
@@ -2072,11 +2084,11 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>42338</v>
       </c>
       <c r="B62" t="n">
-        <v>28.63116836547852</v>
+        <v>28.63117027282715</v>
       </c>
       <c r="C62" t="n">
         <v>36.20000076293945</v>
@@ -2101,11 +2113,11 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>42369</v>
       </c>
       <c r="B63" t="n">
-        <v>27.18237495422363</v>
+        <v>27.18237113952637</v>
       </c>
       <c r="C63" t="n">
         <v>34.0099983215332</v>
@@ -2130,11 +2142,11 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>42400</v>
       </c>
       <c r="B64" t="n">
-        <v>23.68966293334961</v>
+        <v>23.68966865539551</v>
       </c>
       <c r="C64" t="n">
         <v>29.63999938964844</v>
@@ -2159,11 +2171,11 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>42429</v>
       </c>
       <c r="B65" t="n">
-        <v>23.52981185913086</v>
+        <v>23.52981948852539</v>
       </c>
       <c r="C65" t="n">
         <v>29.44000053405762</v>
@@ -2188,11 +2200,11 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>42460</v>
       </c>
       <c r="B66" t="n">
-        <v>25.43535804748535</v>
+        <v>25.43535423278809</v>
       </c>
       <c r="C66" t="n">
         <v>31.43000030517578</v>
@@ -2217,11 +2229,11 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>42490</v>
       </c>
       <c r="B67" t="n">
-        <v>25.73477935791016</v>
+        <v>25.73478507995605</v>
       </c>
       <c r="C67" t="n">
         <v>31.79999923706055</v>
@@ -2246,7 +2258,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>42521</v>
       </c>
       <c r="B68" t="n">
@@ -2275,11 +2287,11 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>42551</v>
       </c>
       <c r="B69" t="n">
-        <v>23.19390106201172</v>
+        <v>23.19389343261719</v>
       </c>
       <c r="C69" t="n">
         <v>28.29999923706055</v>
@@ -2304,11 +2316,11 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>42582</v>
       </c>
       <c r="B70" t="n">
-        <v>25.84930801391602</v>
+        <v>25.84931373596191</v>
       </c>
       <c r="C70" t="n">
         <v>31.54000091552734</v>
@@ -2333,11 +2345,11 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>42613</v>
       </c>
       <c r="B71" t="n">
-        <v>26.16075134277344</v>
+        <v>26.16074752807617</v>
       </c>
       <c r="C71" t="n">
         <v>31.92000007629395</v>
@@ -2362,11 +2374,11 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>42643</v>
       </c>
       <c r="B72" t="n">
-        <v>26.34954452514648</v>
+        <v>26.34954643249512</v>
       </c>
       <c r="C72" t="n">
         <v>31.77000045776367</v>
@@ -2391,7 +2403,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>42674</v>
       </c>
       <c r="B73" t="n">
@@ -2420,11 +2432,11 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>42704</v>
       </c>
       <c r="B74" t="n">
-        <v>28.63864135742188</v>
+        <v>28.63863754272461</v>
       </c>
       <c r="C74" t="n">
         <v>34.52999877929688</v>
@@ -2449,11 +2461,11 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>42735</v>
       </c>
       <c r="B75" t="n">
-        <v>29.2092113494873</v>
+        <v>29.20921325683594</v>
       </c>
       <c r="C75" t="n">
         <v>34.84000015258789</v>
@@ -2478,11 +2490,11 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>42766</v>
       </c>
       <c r="B76" t="n">
-        <v>30.69314765930176</v>
+        <v>30.69314956665039</v>
       </c>
       <c r="C76" t="n">
         <v>36.61000061035156</v>
@@ -2507,11 +2519,11 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="B77" t="n">
-        <v>30.88597297668457</v>
+        <v>30.8859748840332</v>
       </c>
       <c r="C77" t="n">
         <v>36.84000015258789</v>
@@ -2536,11 +2548,11 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="B78" t="n">
-        <v>29.94848823547363</v>
+        <v>29.9484806060791</v>
       </c>
       <c r="C78" t="n">
         <v>35.36000061035156</v>
@@ -2565,11 +2577,11 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>42855</v>
       </c>
       <c r="B79" t="n">
-        <v>29.33866691589355</v>
+        <v>29.33866882324219</v>
       </c>
       <c r="C79" t="n">
         <v>34.63999938964844</v>
@@ -2594,11 +2606,11 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>42886</v>
       </c>
       <c r="B80" t="n">
-        <v>28.73734283447266</v>
+        <v>28.73733139038086</v>
       </c>
       <c r="C80" t="n">
         <v>33.93000030517578</v>
@@ -2623,11 +2635,11 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="B81" t="n">
-        <v>29.91444969177246</v>
+        <v>29.91445350646973</v>
       </c>
       <c r="C81" t="n">
         <v>34.93000030517578</v>
@@ -2652,11 +2664,11 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>42947</v>
       </c>
       <c r="B82" t="n">
-        <v>30.81369400024414</v>
+        <v>30.81368255615234</v>
       </c>
       <c r="C82" t="n">
         <v>35.97999954223633</v>
@@ -2681,11 +2693,11 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>42978</v>
       </c>
       <c r="B83" t="n">
-        <v>31.29327011108398</v>
+        <v>31.29327774047852</v>
       </c>
       <c r="C83" t="n">
         <v>36.54000091552734</v>
@@ -2710,11 +2722,11 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>43008</v>
       </c>
       <c r="B84" t="n">
-        <v>34.93430328369141</v>
+        <v>34.93429946899414</v>
       </c>
       <c r="C84" t="n">
         <v>40.38000106811523</v>
@@ -2739,7 +2751,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="B85" t="n">
@@ -2768,7 +2780,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>43069</v>
       </c>
       <c r="B86" t="n">
@@ -2797,7 +2809,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>43100</v>
       </c>
       <c r="B87" t="n">
@@ -2826,7 +2838,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>43131</v>
       </c>
       <c r="B88" t="n">
@@ -2855,11 +2867,11 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="B89" t="n">
-        <v>34.35292053222656</v>
+        <v>34.3529167175293</v>
       </c>
       <c r="C89" t="n">
         <v>39.34999847412109</v>
@@ -2882,11 +2894,11 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>43190</v>
       </c>
       <c r="B90" t="n">
-        <v>32.04784774780273</v>
+        <v>32.0478401184082</v>
       </c>
       <c r="C90" t="n">
         <v>36.34000015258789</v>
@@ -2909,11 +2921,11 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>43220</v>
       </c>
       <c r="B91" t="n">
-        <v>32.40060043334961</v>
+        <v>32.40059661865234</v>
       </c>
       <c r="C91" t="n">
         <v>36.7400016784668</v>
@@ -2936,11 +2948,11 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>43251</v>
       </c>
       <c r="B92" t="n">
-        <v>37.65665817260742</v>
+        <v>37.65664291381836</v>
       </c>
       <c r="C92" t="n">
         <v>42.70000076293945</v>
@@ -2963,11 +2975,11 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>43281</v>
       </c>
       <c r="B93" t="n">
-        <v>35.04959487915039</v>
+        <v>35.04961013793945</v>
       </c>
       <c r="C93" t="n">
         <v>39.40000152587891</v>
@@ -2990,11 +3002,11 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="B94" t="n">
-        <v>33.7241325378418</v>
+        <v>33.72412490844727</v>
       </c>
       <c r="C94" t="n">
         <v>37.90999984741211</v>
@@ -3017,11 +3029,11 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="B95" t="n">
-        <v>32.06949234008789</v>
+        <v>32.06949615478516</v>
       </c>
       <c r="C95" t="n">
         <v>36.04999923706055</v>
@@ -3044,11 +3056,11 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>43373</v>
       </c>
       <c r="B96" t="n">
-        <v>30.27831649780273</v>
+        <v>30.2783203125</v>
       </c>
       <c r="C96" t="n">
         <v>33.66999816894531</v>
@@ -3071,11 +3083,11 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="B97" t="n">
-        <v>32.90417861938477</v>
+        <v>32.9041862487793</v>
       </c>
       <c r="C97" t="n">
         <v>36.59000015258789</v>
@@ -3100,11 +3112,11 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>43434</v>
       </c>
       <c r="B98" t="n">
-        <v>34.127197265625</v>
+        <v>34.12720108032227</v>
       </c>
       <c r="C98" t="n">
         <v>37.95000076293945</v>
@@ -3129,11 +3141,11 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>43465</v>
       </c>
       <c r="B99" t="n">
-        <v>30.39678001403809</v>
+        <v>30.39677238464355</v>
       </c>
       <c r="C99" t="n">
         <v>33.45000076293945</v>
@@ -3158,11 +3170,11 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="B100" t="n">
-        <v>35.45837020874023</v>
+        <v>35.45835876464844</v>
       </c>
       <c r="C100" t="n">
         <v>39.02000045776367</v>
@@ -3187,7 +3199,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="B101" t="n">
@@ -3216,7 +3228,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>43555</v>
       </c>
       <c r="B102" t="n">
@@ -3245,11 +3257,11 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="B103" t="n">
-        <v>35.74600982666016</v>
+        <v>35.74601364135742</v>
       </c>
       <c r="C103" t="n">
         <v>38.95000076293945</v>
@@ -3274,7 +3286,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>43616</v>
       </c>
       <c r="B104" t="n">
@@ -3303,7 +3315,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>43646</v>
       </c>
       <c r="B105" t="n">
@@ -3332,11 +3344,11 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="B106" t="n">
-        <v>37.41841125488281</v>
+        <v>37.41840744018555</v>
       </c>
       <c r="C106" t="n">
         <v>40.34000015258789</v>
@@ -3361,11 +3373,11 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>43708</v>
       </c>
       <c r="B107" t="n">
-        <v>34.40379333496094</v>
+        <v>34.40378570556641</v>
       </c>
       <c r="C107" t="n">
         <v>37.09000015258789</v>
@@ -3390,7 +3402,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>43738</v>
       </c>
       <c r="B108" t="n">
@@ -3419,11 +3431,11 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="B109" t="n">
-        <v>34.81467056274414</v>
+        <v>34.81468200683594</v>
       </c>
       <c r="C109" t="n">
         <v>37.15999984741211</v>
@@ -3448,11 +3460,11 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>43799</v>
       </c>
       <c r="B110" t="n">
-        <v>33.72788238525391</v>
+        <v>33.7278938293457</v>
       </c>
       <c r="C110" t="n">
         <v>36</v>
@@ -3477,11 +3489,11 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>43830</v>
       </c>
       <c r="B111" t="n">
-        <v>34.65790176391602</v>
+        <v>34.65789794921875</v>
       </c>
       <c r="C111" t="n">
         <v>36.59999847412109</v>
@@ -3506,7 +3518,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="B112" t="n">
@@ -3535,7 +3547,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>43890</v>
       </c>
       <c r="B113" t="n">
@@ -3564,7 +3576,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>43921</v>
       </c>
       <c r="B114" t="n">
@@ -3593,7 +3605,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="B115" t="n">
@@ -3622,11 +3634,11 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>43982</v>
       </c>
       <c r="B116" t="n">
-        <v>24.80569076538086</v>
+        <v>24.80568885803223</v>
       </c>
       <c r="C116" t="n">
         <v>25.8799991607666</v>
@@ -3651,7 +3663,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>44012</v>
       </c>
       <c r="B117" t="n">
@@ -3680,11 +3692,11 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="B118" t="n">
-        <v>23.85678672790527</v>
+        <v>23.85678482055664</v>
       </c>
       <c r="C118" t="n">
         <v>24.88999938964844</v>
@@ -3709,11 +3721,11 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>44074</v>
       </c>
       <c r="B119" t="n">
-        <v>28.40002250671387</v>
+        <v>28.40002632141113</v>
       </c>
       <c r="C119" t="n">
         <v>29.6299991607666</v>
@@ -3738,11 +3750,11 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>44104</v>
       </c>
       <c r="B120" t="n">
-        <v>28.36168479919434</v>
+        <v>28.36168670654297</v>
       </c>
       <c r="C120" t="n">
         <v>29.59000015258789</v>
@@ -3767,11 +3779,11 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>44135</v>
       </c>
       <c r="B121" t="n">
-        <v>33.09662628173828</v>
+        <v>33.09661865234375</v>
       </c>
       <c r="C121" t="n">
         <v>34.52999877929688</v>
@@ -3796,11 +3808,11 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>44165</v>
       </c>
       <c r="B122" t="n">
-        <v>42.0201416015625</v>
+        <v>42.0201530456543</v>
       </c>
       <c r="C122" t="n">
         <v>43.84000015258789</v>
@@ -3825,11 +3837,11 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>44196</v>
       </c>
       <c r="B123" t="n">
-        <v>39.91146850585938</v>
+        <v>39.91146469116211</v>
       </c>
       <c r="C123" t="n">
         <v>41.63999938964844</v>
@@ -3854,11 +3866,11 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>44227</v>
       </c>
       <c r="B124" t="n">
-        <v>48.57621383666992</v>
+        <v>48.57621002197266</v>
       </c>
       <c r="C124" t="n">
         <v>50.68000030517578</v>
@@ -3883,11 +3895,11 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>44255</v>
       </c>
       <c r="B125" t="n">
-        <v>49.19923400878906</v>
+        <v>49.19923782348633</v>
       </c>
       <c r="C125" t="n">
         <v>51.33000183105469</v>
@@ -3912,7 +3924,7 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="B126" t="n">
@@ -3941,11 +3953,11 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B127" t="n">
-        <v>54.84473419189453</v>
+        <v>54.84473037719727</v>
       </c>
       <c r="C127" t="n">
         <v>57.22000122070312</v>
@@ -3970,11 +3982,11 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>44347</v>
       </c>
       <c r="B128" t="n">
-        <v>56.84798431396484</v>
+        <v>56.84797286987305</v>
       </c>
       <c r="C128" t="n">
         <v>59.31000137329102</v>
@@ -3999,11 +4011,11 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="B129" t="n">
-        <v>56.71377944946289</v>
+        <v>56.71378326416016</v>
       </c>
       <c r="C129" t="n">
         <v>59.16999816894531</v>
@@ -4028,11 +4040,11 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>44408</v>
       </c>
       <c r="B130" t="n">
-        <v>54.48050308227539</v>
+        <v>54.48050689697266</v>
       </c>
       <c r="C130" t="n">
         <v>56.84000015258789</v>
@@ -4057,7 +4069,7 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>44439</v>
       </c>
       <c r="B131" t="n">
@@ -4086,11 +4098,11 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="B132" t="n">
-        <v>50.52194595336914</v>
+        <v>50.52195358276367</v>
       </c>
       <c r="C132" t="n">
         <v>52.70999908447266</v>
@@ -4115,11 +4127,11 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>44500</v>
       </c>
       <c r="B133" t="n">
-        <v>52.1705436706543</v>
+        <v>52.17054748535156</v>
       </c>
       <c r="C133" t="n">
         <v>54.43000030517578</v>
@@ -4144,11 +4156,11 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>44530</v>
       </c>
       <c r="B134" t="n">
-        <v>55.46774291992188</v>
+        <v>55.46774673461914</v>
       </c>
       <c r="C134" t="n">
         <v>57.86999893188477</v>
@@ -4173,7 +4185,7 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B135" t="n">
@@ -4202,11 +4214,11 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>44592</v>
       </c>
       <c r="B136" t="n">
-        <v>50.54111099243164</v>
+        <v>50.54110717773438</v>
       </c>
       <c r="C136" t="n">
         <v>52.72999954223633</v>
@@ -4231,11 +4243,11 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B137" t="n">
-        <v>44.78059768676758</v>
+        <v>44.78060531616211</v>
       </c>
       <c r="C137" t="n">
         <v>46.72000122070312</v>
@@ -4260,11 +4272,11 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="B138" t="n">
-        <v>41.92430877685547</v>
+        <v>41.92430114746094</v>
       </c>
       <c r="C138" t="n">
         <v>43.7400016784668</v>
@@ -4289,11 +4301,11 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>44681</v>
       </c>
       <c r="B139" t="n">
-        <v>36.3363151550293</v>
+        <v>36.33631134033203</v>
       </c>
       <c r="C139" t="n">
         <v>37.90999984741211</v>
@@ -4318,11 +4330,11 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>44712</v>
       </c>
       <c r="B140" t="n">
-        <v>37.07435607910156</v>
+        <v>37.07434463500977</v>
       </c>
       <c r="C140" t="n">
         <v>38.68000030517578</v>
@@ -4347,7 +4359,7 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="B141" t="n">
@@ -4376,11 +4388,11 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>44773</v>
       </c>
       <c r="B142" t="n">
-        <v>34.75480651855469</v>
+        <v>34.75480270385742</v>
       </c>
       <c r="C142" t="n">
         <v>36.2599983215332</v>
@@ -4405,11 +4417,11 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>44804</v>
       </c>
       <c r="B143" t="n">
-        <v>36.70747756958008</v>
+        <v>36.70746994018555</v>
       </c>
       <c r="C143" t="n">
         <v>38.20999908447266</v>
@@ -4434,11 +4446,11 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B144" t="n">
-        <v>30.8281307220459</v>
+        <v>30.82813453674316</v>
       </c>
       <c r="C144" t="n">
         <v>32.09000015258789</v>
@@ -4463,7 +4475,7 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="B145" t="n">
@@ -4492,11 +4504,11 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>44895</v>
       </c>
       <c r="B146" t="n">
-        <v>38.96506500244141</v>
+        <v>38.96506118774414</v>
       </c>
       <c r="C146" t="n">
         <v>40.56000137329102</v>
@@ -4521,7 +4533,7 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="B147" t="n">
@@ -4550,11 +4562,11 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="B148" t="n">
-        <v>37.85783767700195</v>
+        <v>37.85782623291016</v>
       </c>
       <c r="C148" t="n">
         <v>39.31999969482422</v>
@@ -4579,11 +4591,11 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B149" t="n">
-        <v>37.29939651489258</v>
+        <v>37.29940032958984</v>
       </c>
       <c r="C149" t="n">
         <v>38.7400016784668</v>
@@ -4608,11 +4620,11 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B150" t="n">
-        <v>35.39828491210938</v>
+        <v>35.39828872680664</v>
       </c>
       <c r="C150" t="n">
         <v>36.68000030517578</v>
@@ -4637,11 +4649,11 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>45046</v>
       </c>
       <c r="B151" t="n">
-        <v>31.88547134399414</v>
+        <v>31.88547515869141</v>
       </c>
       <c r="C151" t="n">
         <v>33.04000091552734</v>
@@ -4666,7 +4678,7 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>45077</v>
       </c>
       <c r="B152" t="n">
@@ -4695,11 +4707,11 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B153" t="n">
-        <v>37.31621551513672</v>
+        <v>37.31621170043945</v>
       </c>
       <c r="C153" t="n">
         <v>38.56000137329102</v>
@@ -4724,11 +4736,11 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="B154" t="n">
-        <v>37.13234710693359</v>
+        <v>37.13233947753906</v>
       </c>
       <c r="C154" t="n">
         <v>38.36999893188477</v>
@@ -4753,11 +4765,11 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="B155" t="n">
-        <v>32.51675033569336</v>
+        <v>32.51675796508789</v>
       </c>
       <c r="C155" t="n">
         <v>33.5099983215332</v>
@@ -4782,11 +4794,11 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="B156" t="n">
-        <v>31.99275779724121</v>
+        <v>31.99276161193848</v>
       </c>
       <c r="C156" t="n">
         <v>32.97000122070312</v>
@@ -4811,11 +4823,11 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="B157" t="n">
-        <v>27.36414527893066</v>
+        <v>27.36414337158203</v>
       </c>
       <c r="C157" t="n">
         <v>28.20000076293945</v>
@@ -4840,11 +4852,11 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="B158" t="n">
-        <v>30.75094604492188</v>
+        <v>30.75094795227051</v>
       </c>
       <c r="C158" t="n">
         <v>31.60000038146973</v>
@@ -4869,11 +4881,11 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="B159" t="n">
-        <v>34.95487594604492</v>
+        <v>34.95487213134766</v>
       </c>
       <c r="C159" t="n">
         <v>35.91999816894531</v>
@@ -4898,11 +4910,11 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="B160" t="n">
-        <v>37.75749969482422</v>
+        <v>37.75749206542969</v>
       </c>
       <c r="C160" t="n">
         <v>38.79999923706055</v>
@@ -4927,11 +4939,11 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="B161" t="n">
-        <v>39.99705123901367</v>
+        <v>39.99704742431641</v>
       </c>
       <c r="C161" t="n">
         <v>40.97999954223633</v>
@@ -4956,11 +4968,11 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="B162" t="n">
-        <v>44.26222610473633</v>
+        <v>44.26222991943359</v>
       </c>
       <c r="C162" t="n">
         <v>45.34999847412109</v>
@@ -4985,11 +4997,11 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="B163" t="n">
-        <v>43.46189880371094</v>
+        <v>43.46189498901367</v>
       </c>
       <c r="C163" t="n">
         <v>44.52999877929688</v>
@@ -5014,7 +5026,7 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B164" t="n">
@@ -5043,7 +5055,7 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B165" t="n">
@@ -5072,11 +5084,11 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="B166" t="n">
-        <v>43.37104797363281</v>
+        <v>43.37104415893555</v>
       </c>
       <c r="C166" t="n">
         <v>44.31999969482422</v>
@@ -5101,11 +5113,11 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>45535</v>
       </c>
       <c r="B167" t="n">
-        <v>48.71414184570312</v>
+        <v>48.71413421630859</v>
       </c>
       <c r="C167" t="n">
         <v>49.77999877929688</v>
@@ -5130,7 +5142,7 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B168" t="n">
@@ -5159,7 +5171,7 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="B169" t="n">
@@ -5188,11 +5200,11 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>45626</v>
       </c>
       <c r="B170" t="n">
-        <v>54.53564834594727</v>
+        <v>54.53565216064453</v>
       </c>
       <c r="C170" t="n">
         <v>55.59000015258789</v>
@@ -5217,7 +5229,7 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="B171" t="n">
@@ -5246,7 +5258,7 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B172" t="n">
@@ -5275,7 +5287,7 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B173" t="n">
@@ -5304,11 +5316,11 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="B174" t="n">
-        <v>46.35979843139648</v>
+        <v>46.35980224609375</v>
       </c>
       <c r="C174" t="n">
         <v>47.02999877929688</v>
@@ -5333,11 +5345,11 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="B175" t="n">
-        <v>44.59531402587891</v>
+        <v>44.59531021118164</v>
       </c>
       <c r="C175" t="n">
         <v>45.2400016784668</v>
@@ -5362,7 +5374,7 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>45808</v>
       </c>
       <c r="B176" t="n">
@@ -5391,11 +5403,11 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B177" t="n">
-        <v>48.66322708129883</v>
+        <v>48.66322326660156</v>
       </c>
       <c r="C177" t="n">
         <v>49.20999908447266</v>
@@ -5420,7 +5432,7 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="B178" t="n">
@@ -5449,11 +5461,11 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="B179" t="n">
-        <v>57.93899917602539</v>
+        <v>57.93900299072266</v>
       </c>
       <c r="C179" t="n">
         <v>58.59000015258789</v>
@@ -5478,7 +5490,7 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="B180" t="n">
@@ -5507,11 +5519,11 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B181" t="n">
-        <v>68.49901580810547</v>
+        <v>68.49903106689453</v>
       </c>
       <c r="C181" t="n">
         <v>69.08999633789062</v>
@@ -5536,7 +5548,7 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="B182" t="n">
@@ -5565,7 +5577,7 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="B183" t="n">
@@ -5594,7 +5606,7 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="B184" t="n">
@@ -5623,11 +5635,11 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="B185" t="n">
-        <v>78.19252777099609</v>
+        <v>78.19252014160156</v>
       </c>
       <c r="C185" t="n">
         <v>78.70999908447266</v>
@@ -5652,11 +5664,11 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="B186" t="n">
-        <v>74.18544769287109</v>
+        <v>74.18544006347656</v>
       </c>
       <c r="C186" t="n">
         <v>74.5</v>
@@ -5681,7 +5693,7 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="B187" t="n">
@@ -5710,11 +5722,11 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>46173</v>
       </c>
       <c r="B188" t="n">
-        <v>82.88854217529297</v>
+        <v>82.88853454589844</v>
       </c>
       <c r="C188" t="n">
         <v>83.23999786376953</v>
@@ -5739,7 +5751,7 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="B189" t="n">
@@ -5768,7 +5780,7 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B190" t="n">
@@ -5797,7 +5809,7 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="B191" t="n">
@@ -5826,32 +5838,32 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>46295</v>
       </c>
       <c r="B192" t="n">
-        <v>83.76999664306641</v>
+        <v>80.56999969482422</v>
       </c>
       <c r="C192" t="n">
-        <v>83.76999664306641</v>
+        <v>80.56999969482422</v>
       </c>
       <c r="D192" t="n">
-        <v>116588100</v>
+        <v>124523000</v>
       </c>
       <c r="E192" t="n">
         <v>2.24</v>
       </c>
       <c r="F192" t="n">
-        <v>37.39731992994036</v>
+        <v>35.96874986376081</v>
       </c>
       <c r="G192" t="n">
         <v>877451541</v>
       </c>
       <c r="H192" t="n">
-        <v>73504112644.02344</v>
+        <v>70696270390.59305</v>
       </c>
       <c r="I192" t="n">
-        <v>0.1328712692978221</v>
+        <v>0.1419143897771102</v>
       </c>
     </row>
   </sheetData>
@@ -5883,75 +5895,75 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>start</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>eps_trimestral</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>origen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>filed_ttm</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>40179</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>40268</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="2" t="n">
         <v>40966</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -5987,13 +5999,13 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>40269</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>40359</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="2" t="n">
         <v>40760</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -6029,13 +6041,13 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>40360</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>40451</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="2" t="n">
         <v>40856</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -6071,13 +6083,13 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>40452</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>40543</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="2" t="n">
         <v>40966</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -6104,7 +6116,7 @@
       <c r="I5" t="n">
         <v>2.91</v>
       </c>
-      <c r="J5" s="1" t="n">
+      <c r="J5" s="2" t="n">
         <v>40966</v>
       </c>
       <c r="K5" t="n">
@@ -6117,13 +6129,13 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40544</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40633</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="2" t="n">
         <v>40966</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -6150,7 +6162,7 @@
       <c r="I6" t="n">
         <v>4.130000000000001</v>
       </c>
-      <c r="J6" s="1" t="n">
+      <c r="J6" s="2" t="n">
         <v>40966</v>
       </c>
       <c r="K6" t="n">
@@ -6163,13 +6175,13 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40634</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40724</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="2" t="n">
         <v>40760</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -6196,7 +6208,7 @@
       <c r="I7" t="n">
         <v>4.82</v>
       </c>
-      <c r="J7" s="1" t="n">
+      <c r="J7" s="2" t="n">
         <v>40966</v>
       </c>
       <c r="K7" t="n">
@@ -6209,13 +6221,13 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40725</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40816</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="2" t="n">
         <v>40856</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -6242,7 +6254,7 @@
       <c r="I8" t="n">
         <v>4.65</v>
       </c>
-      <c r="J8" s="1" t="n">
+      <c r="J8" s="2" t="n">
         <v>40966</v>
       </c>
       <c r="K8" t="n">
@@ -6255,13 +6267,13 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40817</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40908</v>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="C9" s="2" t="n">
         <v>40966</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -6288,7 +6300,7 @@
       <c r="I9" t="n">
         <v>4.620000000000001</v>
       </c>
-      <c r="J9" s="1" t="n">
+      <c r="J9" s="2" t="n">
         <v>40966</v>
       </c>
       <c r="K9" t="n">
@@ -6301,13 +6313,13 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40909</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40999</v>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="C10" s="2" t="n">
         <v>41320</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -6334,7 +6346,7 @@
       <c r="I10" t="n">
         <v>3.45</v>
       </c>
-      <c r="J10" s="1" t="n">
+      <c r="J10" s="2" t="n">
         <v>41320</v>
       </c>
       <c r="K10" t="n">
@@ -6347,13 +6359,13 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>41000</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>41090</v>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" s="2" t="n">
         <v>41320</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -6380,7 +6392,7 @@
       <c r="I11" t="n">
         <v>2.81</v>
       </c>
-      <c r="J11" s="1" t="n">
+      <c r="J11" s="2" t="n">
         <v>41320</v>
       </c>
       <c r="K11" t="n">
@@ -6393,13 +6405,13 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>41091</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>41182</v>
       </c>
-      <c r="C12" s="1" t="n">
+      <c r="C12" s="2" t="n">
         <v>41213</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -6426,7 +6438,7 @@
       <c r="I12" t="n">
         <v>2.67</v>
       </c>
-      <c r="J12" s="1" t="n">
+      <c r="J12" s="2" t="n">
         <v>41320</v>
       </c>
       <c r="K12" t="n">
@@ -6439,13 +6451,13 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>41183</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>41274</v>
       </c>
-      <c r="C13" s="1" t="n">
+      <c r="C13" s="2" t="n">
         <v>41320</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -6472,7 +6484,7 @@
       <c r="I13" t="n">
         <v>2.93</v>
       </c>
-      <c r="J13" s="1" t="n">
+      <c r="J13" s="2" t="n">
         <v>41320</v>
       </c>
       <c r="K13" t="n">
@@ -6485,13 +6497,13 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>41275</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>41364</v>
       </c>
-      <c r="C14" s="1" t="n">
+      <c r="C14" s="2" t="n">
         <v>41676</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -6518,7 +6530,7 @@
       <c r="I14" t="n">
         <v>2.91</v>
       </c>
-      <c r="J14" s="1" t="n">
+      <c r="J14" s="2" t="n">
         <v>41676</v>
       </c>
       <c r="K14" t="n">
@@ -6531,13 +6543,13 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>41365</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>41455</v>
       </c>
-      <c r="C15" s="1" t="n">
+      <c r="C15" s="2" t="n">
         <v>41480</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -6564,7 +6576,7 @@
       <c r="I15" t="n">
         <v>2.76</v>
       </c>
-      <c r="J15" s="1" t="n">
+      <c r="J15" s="2" t="n">
         <v>41676</v>
       </c>
       <c r="K15" t="n">
@@ -6577,13 +6589,13 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41456</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41547</v>
       </c>
-      <c r="C16" s="1" t="n">
+      <c r="C16" s="2" t="n">
         <v>41577</v>
       </c>
       <c r="D16" t="inlineStr">
@@ -6610,7 +6622,7 @@
       <c r="I16" t="n">
         <v>2.32</v>
       </c>
-      <c r="J16" s="1" t="n">
+      <c r="J16" s="2" t="n">
         <v>41676</v>
       </c>
       <c r="K16" t="n">
@@ -6623,13 +6635,13 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41548</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41639</v>
       </c>
-      <c r="C17" s="1" t="n">
+      <c r="C17" s="2" t="n">
         <v>41676</v>
       </c>
       <c r="D17" t="inlineStr">
@@ -6656,7 +6668,7 @@
       <c r="I17" t="n">
         <v>2.35</v>
       </c>
-      <c r="J17" s="1" t="n">
+      <c r="J17" s="2" t="n">
         <v>41676</v>
       </c>
       <c r="K17" t="n">
@@ -6669,13 +6681,13 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41640</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41729</v>
       </c>
-      <c r="C18" s="1" t="n">
+      <c r="C18" s="2" t="n">
         <v>41753</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -6702,7 +6714,7 @@
       <c r="I18" t="n">
         <v>1.83</v>
       </c>
-      <c r="J18" s="1" t="n">
+      <c r="J18" s="2" t="n">
         <v>41753</v>
       </c>
       <c r="K18" t="n">
@@ -6715,13 +6727,13 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41730</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41820</v>
       </c>
-      <c r="C19" s="1" t="n">
+      <c r="C19" s="2" t="n">
         <v>41844</v>
       </c>
       <c r="D19" t="inlineStr">
@@ -6748,7 +6760,7 @@
       <c r="I19" t="n">
         <v>1.19</v>
       </c>
-      <c r="J19" s="1" t="n">
+      <c r="J19" s="2" t="n">
         <v>41844</v>
       </c>
       <c r="K19" t="n">
@@ -6761,13 +6773,13 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41821</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41912</v>
       </c>
-      <c r="C20" s="1" t="n">
+      <c r="C20" s="2" t="n">
         <v>41935</v>
       </c>
       <c r="D20" t="inlineStr">
@@ -6794,7 +6806,7 @@
       <c r="I20" t="n">
         <v>1.55</v>
       </c>
-      <c r="J20" s="1" t="n">
+      <c r="J20" s="2" t="n">
         <v>41935</v>
       </c>
       <c r="K20" t="n">
@@ -6807,13 +6819,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41913</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>42004</v>
       </c>
-      <c r="C21" s="1" t="n">
+      <c r="C21" s="2" t="n">
         <v>42039</v>
       </c>
       <c r="D21" t="inlineStr">
@@ -6840,7 +6852,7 @@
       <c r="I21" t="n">
         <v>1.64</v>
       </c>
-      <c r="J21" s="1" t="n">
+      <c r="J21" s="2" t="n">
         <v>42039</v>
       </c>
       <c r="K21" t="n">
@@ -6853,13 +6865,13 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>42005</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>42094</v>
       </c>
-      <c r="C22" s="1" t="n">
+      <c r="C22" s="2" t="n">
         <v>42117</v>
       </c>
       <c r="D22" t="inlineStr">
@@ -6886,7 +6898,7 @@
       <c r="I22" t="n">
         <v>2.14</v>
       </c>
-      <c r="J22" s="1" t="n">
+      <c r="J22" s="2" t="n">
         <v>42117</v>
       </c>
       <c r="K22" t="n">
@@ -6899,13 +6911,13 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>42095</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>42185</v>
       </c>
-      <c r="C23" s="1" t="n">
+      <c r="C23" s="2" t="n">
         <v>42208</v>
       </c>
       <c r="D23" t="inlineStr">
@@ -6932,7 +6944,7 @@
       <c r="I23" t="n">
         <v>2.7</v>
       </c>
-      <c r="J23" s="1" t="n">
+      <c r="J23" s="2" t="n">
         <v>42208</v>
       </c>
       <c r="K23" t="n">
@@ -6945,13 +6957,13 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>42186</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>42277</v>
       </c>
-      <c r="C24" s="1" t="n">
+      <c r="C24" s="2" t="n">
         <v>42298</v>
       </c>
       <c r="D24" t="inlineStr">
@@ -6978,7 +6990,7 @@
       <c r="I24" t="n">
         <v>2.73</v>
       </c>
-      <c r="J24" s="1" t="n">
+      <c r="J24" s="2" t="n">
         <v>42298</v>
       </c>
       <c r="K24" t="n">
@@ -6991,13 +7003,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>42278</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>42369</v>
       </c>
-      <c r="C25" s="1" t="n">
+      <c r="C25" s="2" t="n">
         <v>42403</v>
       </c>
       <c r="D25" t="inlineStr">
@@ -7024,7 +7036,7 @@
       <c r="I25" t="n">
         <v>5.99</v>
       </c>
-      <c r="J25" s="1" t="n">
+      <c r="J25" s="2" t="n">
         <v>42403</v>
       </c>
       <c r="K25" t="n">
@@ -7037,13 +7049,13 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>42370</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42460</v>
       </c>
-      <c r="C26" s="1" t="n">
+      <c r="C26" s="2" t="n">
         <v>42481</v>
       </c>
       <c r="D26" t="inlineStr">
@@ -7070,7 +7082,7 @@
       <c r="I26" t="n">
         <v>6.67</v>
       </c>
-      <c r="J26" s="1" t="n">
+      <c r="J26" s="2" t="n">
         <v>42481</v>
       </c>
       <c r="K26" t="n">
@@ -7083,13 +7095,13 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42461</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42551</v>
       </c>
-      <c r="C27" s="1" t="n">
+      <c r="C27" s="2" t="n">
         <v>42572</v>
       </c>
       <c r="D27" t="inlineStr">
@@ -7116,7 +7128,7 @@
       <c r="I27" t="n">
         <v>7.81</v>
       </c>
-      <c r="J27" s="1" t="n">
+      <c r="J27" s="2" t="n">
         <v>42572</v>
       </c>
       <c r="K27" t="n">
@@ -7129,13 +7141,13 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42552</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42643</v>
       </c>
-      <c r="C28" s="1" t="n">
+      <c r="C28" s="2" t="n">
         <v>42668</v>
       </c>
       <c r="D28" t="inlineStr">
@@ -7162,7 +7174,7 @@
       <c r="I28" t="n">
         <v>8.73</v>
       </c>
-      <c r="J28" s="1" t="n">
+      <c r="J28" s="2" t="n">
         <v>42668</v>
       </c>
       <c r="K28" t="n">
@@ -7175,13 +7187,13 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42644</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42735</v>
       </c>
-      <c r="C29" s="1" t="n">
+      <c r="C29" s="2" t="n">
         <v>42773</v>
       </c>
       <c r="D29" t="inlineStr">
@@ -7208,7 +7220,7 @@
       <c r="I29" t="n">
         <v>6</v>
       </c>
-      <c r="J29" s="1" t="n">
+      <c r="J29" s="2" t="n">
         <v>42773</v>
       </c>
       <c r="K29" t="n">
@@ -7221,13 +7233,13 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42736</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42825</v>
       </c>
-      <c r="C30" s="1" t="n">
+      <c r="C30" s="2" t="n">
         <v>42853</v>
       </c>
       <c r="D30" t="inlineStr">
@@ -7254,7 +7266,7 @@
       <c r="I30" t="n">
         <v>6.46</v>
       </c>
-      <c r="J30" s="1" t="n">
+      <c r="J30" s="2" t="n">
         <v>42853</v>
       </c>
       <c r="K30" t="n">
@@ -7267,13 +7279,13 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42826</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42916</v>
       </c>
-      <c r="C31" s="1" t="n">
+      <c r="C31" s="2" t="n">
         <v>42941</v>
       </c>
       <c r="D31" t="inlineStr">
@@ -7300,7 +7312,7 @@
       <c r="I31" t="n">
         <v>5.74</v>
       </c>
-      <c r="J31" s="1" t="n">
+      <c r="J31" s="2" t="n">
         <v>42941</v>
       </c>
       <c r="K31" t="n">
@@ -7313,13 +7325,13 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42917</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>43008</v>
       </c>
-      <c r="C32" s="1" t="n">
+      <c r="C32" s="2" t="n">
         <v>43032</v>
       </c>
       <c r="D32" t="inlineStr">
@@ -7346,7 +7358,7 @@
       <c r="I32" t="n">
         <v>1.95</v>
       </c>
-      <c r="J32" s="1" t="n">
+      <c r="J32" s="2" t="n">
         <v>43032</v>
       </c>
       <c r="K32" t="n">
@@ -7359,13 +7371,13 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>43009</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>43100</v>
       </c>
-      <c r="C33" s="1" t="n">
+      <c r="C33" s="2" t="n">
         <v>43137</v>
       </c>
       <c r="D33" t="inlineStr">
@@ -7392,7 +7404,7 @@
       <c r="I33" t="n">
         <v>-2.6</v>
       </c>
-      <c r="J33" s="1" t="n">
+      <c r="J33" s="2" t="n">
         <v>43137</v>
       </c>
       <c r="K33" t="n">
@@ -7405,13 +7417,13 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>43101</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>43190</v>
       </c>
-      <c r="C34" s="1" t="n">
+      <c r="C34" s="2" t="n">
         <v>43216</v>
       </c>
       <c r="D34" t="inlineStr">
@@ -7438,7 +7450,7 @@
       <c r="I34" t="n">
         <v>-3.58</v>
       </c>
-      <c r="J34" s="1" t="n">
+      <c r="J34" s="2" t="n">
         <v>43216</v>
       </c>
       <c r="K34" t="n">
@@ -7451,13 +7463,13 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>43191</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>43281</v>
       </c>
-      <c r="C35" s="1" t="n">
+      <c r="C35" s="2" t="n">
         <v>43306</v>
       </c>
       <c r="D35" t="inlineStr">
@@ -7484,7 +7496,7 @@
       <c r="I35" t="n">
         <v>-3.01</v>
       </c>
-      <c r="J35" s="1" t="n">
+      <c r="J35" s="2" t="n">
         <v>43306</v>
       </c>
       <c r="K35" t="n">
@@ -7497,13 +7509,13 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>43282</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>43373</v>
       </c>
-      <c r="C36" s="1" t="n">
+      <c r="C36" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="D36" t="inlineStr">
@@ -7530,7 +7542,7 @@
       <c r="I36" t="n">
         <v>0.7699999999999996</v>
       </c>
-      <c r="J36" s="1" t="n">
+      <c r="J36" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="K36" t="n">
@@ -7543,13 +7555,13 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>43374</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43465</v>
       </c>
-      <c r="C37" s="1" t="n">
+      <c r="C37" s="2" t="n">
         <v>43502</v>
       </c>
       <c r="D37" t="inlineStr">
@@ -7576,7 +7588,7 @@
       <c r="I37" t="n">
         <v>5.53</v>
       </c>
-      <c r="J37" s="1" t="n">
+      <c r="J37" s="2" t="n">
         <v>43502</v>
       </c>
       <c r="K37" t="n">
@@ -7589,13 +7601,13 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43466</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43555</v>
       </c>
-      <c r="C38" s="1" t="n">
+      <c r="C38" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="D38" t="inlineStr">
@@ -7622,7 +7634,7 @@
       <c r="I38" t="n">
         <v>6.290000000000001</v>
       </c>
-      <c r="J38" s="1" t="n">
+      <c r="J38" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="K38" t="n">
@@ -7635,13 +7647,13 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43556</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43646</v>
       </c>
-      <c r="C39" s="1" t="n">
+      <c r="C39" s="2" t="n">
         <v>43678</v>
       </c>
       <c r="D39" t="inlineStr">
@@ -7668,7 +7680,7 @@
       <c r="I39" t="n">
         <v>6.29</v>
       </c>
-      <c r="J39" s="1" t="n">
+      <c r="J39" s="2" t="n">
         <v>43678</v>
       </c>
       <c r="K39" t="n">
@@ -7681,13 +7693,13 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43647</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43738</v>
       </c>
-      <c r="C40" s="1" t="n">
+      <c r="C40" s="2" t="n">
         <v>43767</v>
       </c>
       <c r="D40" t="inlineStr">
@@ -7714,7 +7726,7 @@
       <c r="I40" t="n">
         <v>6.140000000000001</v>
       </c>
-      <c r="J40" s="1" t="n">
+      <c r="J40" s="2" t="n">
         <v>43767</v>
       </c>
       <c r="K40" t="n">
@@ -7727,13 +7739,13 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43739</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43830</v>
       </c>
-      <c r="C41" s="1" t="n">
+      <c r="C41" s="2" t="n">
         <v>43866</v>
       </c>
       <c r="D41" t="inlineStr">
@@ -7760,7 +7772,7 @@
       <c r="I41" t="n">
         <v>4.57</v>
       </c>
-      <c r="J41" s="1" t="n">
+      <c r="J41" s="2" t="n">
         <v>43866</v>
       </c>
       <c r="K41" t="n">
@@ -7773,13 +7785,13 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43831</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43921</v>
       </c>
-      <c r="C42" s="1" t="n">
+      <c r="C42" s="2" t="n">
         <v>43957</v>
       </c>
       <c r="D42" t="inlineStr">
@@ -7806,7 +7818,7 @@
       <c r="I42" t="n">
         <v>3.26</v>
       </c>
-      <c r="J42" s="1" t="n">
+      <c r="J42" s="2" t="n">
         <v>43957</v>
       </c>
       <c r="K42" t="n">
@@ -7819,13 +7831,13 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43922</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>44012</v>
       </c>
-      <c r="C43" s="1" t="n">
+      <c r="C43" s="2" t="n">
         <v>44041</v>
       </c>
       <c r="D43" t="inlineStr">
@@ -7852,7 +7864,7 @@
       <c r="I43" t="n">
         <v>1.04</v>
       </c>
-      <c r="J43" s="1" t="n">
+      <c r="J43" s="2" t="n">
         <v>44041</v>
       </c>
       <c r="K43" t="n">
@@ -7865,13 +7877,13 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>44013</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>44104</v>
       </c>
-      <c r="C44" s="1" t="n">
+      <c r="C44" s="2" t="n">
         <v>44140</v>
       </c>
       <c r="D44" t="inlineStr">
@@ -7898,7 +7910,7 @@
       <c r="I44" t="n">
         <v>2.22</v>
       </c>
-      <c r="J44" s="1" t="n">
+      <c r="J44" s="2" t="n">
         <v>44140</v>
       </c>
       <c r="K44" t="n">
@@ -7911,13 +7923,13 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>44105</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>44196</v>
       </c>
-      <c r="C45" s="1" t="n">
+      <c r="C45" s="2" t="n">
         <v>44237</v>
       </c>
       <c r="D45" t="inlineStr">
@@ -7944,7 +7956,7 @@
       <c r="I45" t="n">
         <v>4.33</v>
       </c>
-      <c r="J45" s="1" t="n">
+      <c r="J45" s="2" t="n">
         <v>44237</v>
       </c>
       <c r="K45" t="n">
@@ -7957,13 +7969,13 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>44197</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>44286</v>
       </c>
-      <c r="C46" s="1" t="n">
+      <c r="C46" s="2" t="n">
         <v>44321</v>
       </c>
       <c r="D46" t="inlineStr">
@@ -7990,7 +8002,7 @@
       <c r="I46" t="n">
         <v>6.19</v>
       </c>
-      <c r="J46" s="1" t="n">
+      <c r="J46" s="2" t="n">
         <v>44321</v>
       </c>
       <c r="K46" t="n">
@@ -8003,13 +8015,13 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>44287</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>44377</v>
       </c>
-      <c r="C47" s="1" t="n">
+      <c r="C47" s="2" t="n">
         <v>44412</v>
       </c>
       <c r="D47" t="inlineStr">
@@ -8036,7 +8048,7 @@
       <c r="I47" t="n">
         <v>8.649999999999999</v>
       </c>
-      <c r="J47" s="1" t="n">
+      <c r="J47" s="2" t="n">
         <v>44412</v>
       </c>
       <c r="K47" t="n">
@@ -8049,13 +8061,13 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>44378</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44469</v>
       </c>
-      <c r="C48" s="1" t="n">
+      <c r="C48" s="2" t="n">
         <v>44496</v>
       </c>
       <c r="D48" t="inlineStr">
@@ -8082,7 +8094,7 @@
       <c r="I48" t="n">
         <v>7.49</v>
       </c>
-      <c r="J48" s="1" t="n">
+      <c r="J48" s="2" t="n">
         <v>44496</v>
       </c>
       <c r="K48" t="n">
@@ -8095,13 +8107,13 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44470</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44561</v>
       </c>
-      <c r="C49" s="1" t="n">
+      <c r="C49" s="2" t="n">
         <v>44594</v>
       </c>
       <c r="D49" t="inlineStr">
@@ -8128,7 +8140,7 @@
       <c r="I49" t="n">
         <v>6.7</v>
       </c>
-      <c r="J49" s="1" t="n">
+      <c r="J49" s="2" t="n">
         <v>44594</v>
       </c>
       <c r="K49" t="n">
@@ -8141,13 +8153,13 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44562</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44651</v>
       </c>
-      <c r="C50" s="1" t="n">
+      <c r="C50" s="2" t="n">
         <v>44678</v>
       </c>
       <c r="D50" t="inlineStr">
@@ -8174,7 +8186,7 @@
       <c r="I50" t="n">
         <v>6.02</v>
       </c>
-      <c r="J50" s="1" t="n">
+      <c r="J50" s="2" t="n">
         <v>44678</v>
       </c>
       <c r="K50" t="n">
@@ -8187,13 +8199,13 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44652</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44742</v>
       </c>
-      <c r="C51" s="1" t="n">
+      <c r="C51" s="2" t="n">
         <v>44768</v>
       </c>
       <c r="D51" t="inlineStr">
@@ -8220,7 +8232,7 @@
       <c r="I51" t="n">
         <v>5.260000000000001</v>
       </c>
-      <c r="J51" s="1" t="n">
+      <c r="J51" s="2" t="n">
         <v>44768</v>
       </c>
       <c r="K51" t="n">
@@ -8233,13 +8245,13 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44743</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44834</v>
       </c>
-      <c r="C52" s="1" t="n">
+      <c r="C52" s="2" t="n">
         <v>44859</v>
       </c>
       <c r="D52" t="inlineStr">
@@ -8266,7 +8278,7 @@
       <c r="I52" t="n">
         <v>5.890000000000001</v>
       </c>
-      <c r="J52" s="1" t="n">
+      <c r="J52" s="2" t="n">
         <v>44859</v>
       </c>
       <c r="K52" t="n">
@@ -8279,13 +8291,13 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44835</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44926</v>
       </c>
-      <c r="C53" s="1" t="n">
+      <c r="C53" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="D53" t="inlineStr">
@@ -8312,7 +8324,7 @@
       <c r="I53" t="n">
         <v>6.13</v>
       </c>
-      <c r="J53" s="1" t="n">
+      <c r="J53" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="K53" t="n">
@@ -8325,13 +8337,13 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44927</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>45016</v>
       </c>
-      <c r="C54" s="1" t="n">
+      <c r="C54" s="2" t="n">
         <v>45041</v>
       </c>
       <c r="D54" t="inlineStr">
@@ -8358,7 +8370,7 @@
       <c r="I54" t="n">
         <v>6.469999999999999</v>
       </c>
-      <c r="J54" s="1" t="n">
+      <c r="J54" s="2" t="n">
         <v>45041</v>
       </c>
       <c r="K54" t="n">
@@ -8371,13 +8383,13 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>45017</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>45107</v>
       </c>
-      <c r="C55" s="1" t="n">
+      <c r="C55" s="2" t="n">
         <v>45132</v>
       </c>
       <c r="D55" t="inlineStr">
@@ -8404,7 +8416,7 @@
       <c r="I55" t="n">
         <v>7.16</v>
       </c>
-      <c r="J55" s="1" t="n">
+      <c r="J55" s="2" t="n">
         <v>45132</v>
       </c>
       <c r="K55" t="n">
@@ -8417,13 +8429,13 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>45108</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>45199</v>
       </c>
-      <c r="C56" s="1" t="n">
+      <c r="C56" s="2" t="n">
         <v>45223</v>
       </c>
       <c r="D56" t="inlineStr">
@@ -8450,7 +8462,7 @@
       <c r="I56" t="n">
         <v>7.109999999999999</v>
       </c>
-      <c r="J56" s="1" t="n">
+      <c r="J56" s="2" t="n">
         <v>45223</v>
       </c>
       <c r="K56" t="n">
@@ -8463,13 +8475,13 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>45200</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>45291</v>
       </c>
-      <c r="C57" s="1" t="n">
+      <c r="C57" s="2" t="n">
         <v>45321</v>
       </c>
       <c r="D57" t="inlineStr">
@@ -8496,7 +8508,7 @@
       <c r="I57" t="n">
         <v>7.32</v>
       </c>
-      <c r="J57" s="1" t="n">
+      <c r="J57" s="2" t="n">
         <v>45321</v>
       </c>
       <c r="K57" t="n">
@@ -8509,13 +8521,13 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>45292</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>45382</v>
       </c>
-      <c r="C58" s="1" t="n">
+      <c r="C58" s="2" t="n">
         <v>45405</v>
       </c>
       <c r="D58" t="inlineStr">
@@ -8542,7 +8554,7 @@
       <c r="I58" t="n">
         <v>8.190000000000001</v>
       </c>
-      <c r="J58" s="1" t="n">
+      <c r="J58" s="2" t="n">
         <v>45405</v>
       </c>
       <c r="K58" t="n">
@@ -8555,13 +8567,13 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>45383</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45473</v>
       </c>
-      <c r="C59" s="1" t="n">
+      <c r="C59" s="2" t="n">
         <v>45496</v>
       </c>
       <c r="D59" t="inlineStr">
@@ -8588,7 +8600,7 @@
       <c r="I59" t="n">
         <v>8.91</v>
       </c>
-      <c r="J59" s="1" t="n">
+      <c r="J59" s="2" t="n">
         <v>45496</v>
       </c>
       <c r="K59" t="n">
@@ -8601,13 +8613,13 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45474</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45565</v>
       </c>
-      <c r="C60" s="1" t="n">
+      <c r="C60" s="2" t="n">
         <v>45587</v>
       </c>
       <c r="D60" t="inlineStr">
@@ -8634,7 +8646,7 @@
       <c r="I60" t="n">
         <v>9.389999999999999</v>
       </c>
-      <c r="J60" s="1" t="n">
+      <c r="J60" s="2" t="n">
         <v>45587</v>
       </c>
       <c r="K60" t="n">
@@ -8647,13 +8659,13 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45566</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45657</v>
       </c>
-      <c r="C61" s="1" t="n">
+      <c r="C61" s="2" t="n">
         <v>45685</v>
       </c>
       <c r="D61" t="inlineStr">
@@ -8680,7 +8692,7 @@
       <c r="I61" t="n">
         <v>6.370000000000001</v>
       </c>
-      <c r="J61" s="1" t="n">
+      <c r="J61" s="2" t="n">
         <v>45685</v>
       </c>
       <c r="K61" t="n">
@@ -8693,13 +8705,13 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45658</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45747</v>
       </c>
-      <c r="C62" s="1" t="n">
+      <c r="C62" s="2" t="n">
         <v>45778</v>
       </c>
       <c r="D62" t="inlineStr">
@@ -8726,7 +8738,7 @@
       <c r="I62" t="n">
         <v>7.160000000000001</v>
       </c>
-      <c r="J62" s="1" t="n">
+      <c r="J62" s="2" t="n">
         <v>45778</v>
       </c>
       <c r="K62" t="n">
@@ -8739,13 +8751,13 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45748</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45838</v>
       </c>
-      <c r="C63" s="1" t="n">
+      <c r="C63" s="2" t="n">
         <v>45860</v>
       </c>
       <c r="D63" t="inlineStr">
@@ -8772,7 +8784,7 @@
       <c r="I63" t="n">
         <v>6.520000000000001</v>
       </c>
-      <c r="J63" s="1" t="n">
+      <c r="J63" s="2" t="n">
         <v>45860</v>
       </c>
       <c r="K63" t="n">
@@ -8785,13 +8797,13 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45839</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45930</v>
       </c>
-      <c r="C64" s="1" t="n">
+      <c r="C64" s="2" t="n">
         <v>45951</v>
       </c>
       <c r="D64" t="inlineStr">
@@ -8818,7 +8830,7 @@
       <c r="I64" t="n">
         <v>5.190000000000001</v>
       </c>
-      <c r="J64" s="1" t="n">
+      <c r="J64" s="2" t="n">
         <v>45951</v>
       </c>
       <c r="K64" t="n">
@@ -8831,13 +8843,13 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45931</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>46022</v>
       </c>
-      <c r="C65" s="1" t="n">
+      <c r="C65" s="2" t="n">
         <v>46049</v>
       </c>
       <c r="D65" t="inlineStr">
@@ -8864,7 +8876,7 @@
       <c r="I65" t="n">
         <v>3.27</v>
       </c>
-      <c r="J65" s="1" t="n">
+      <c r="J65" s="2" t="n">
         <v>46049</v>
       </c>
       <c r="K65" t="n">
@@ -8877,13 +8889,13 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>46023</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>46112</v>
       </c>
-      <c r="C66" s="1" t="n">
+      <c r="C66" s="2" t="n">
         <v>46140</v>
       </c>
       <c r="D66" t="inlineStr">
@@ -8910,7 +8922,7 @@
       <c r="I66" t="n">
         <v>2.74</v>
       </c>
-      <c r="J66" s="1" t="n">
+      <c r="J66" s="2" t="n">
         <v>46140</v>
       </c>
       <c r="K66" t="n">
@@ -8923,13 +8935,13 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>46113</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>46203</v>
       </c>
-      <c r="C67" s="1" t="n">
+      <c r="C67" s="2" t="n">
         <v>46224</v>
       </c>
       <c r="D67" t="inlineStr">
@@ -8956,7 +8968,7 @@
       <c r="I67" t="n">
         <v>2.24</v>
       </c>
-      <c r="J67" s="1" t="n">
+      <c r="J67" s="2" t="n">
         <v>46224</v>
       </c>
       <c r="K67" t="n">
@@ -8993,52 +9005,52 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>acciones</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>40755</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>40760</v>
       </c>
       <c r="C2" t="n">
@@ -9067,10 +9079,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>40847</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>40856</v>
       </c>
       <c r="C3" t="n">
@@ -9099,10 +9111,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>40954</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>40966</v>
       </c>
       <c r="C4" t="n">
@@ -9131,10 +9143,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>41026</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>41032</v>
       </c>
       <c r="C5" t="n">
@@ -9163,10 +9175,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>41117</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>41124</v>
       </c>
       <c r="C6" t="n">
@@ -9195,10 +9207,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>41208</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>41213</v>
       </c>
       <c r="C7" t="n">
@@ -9227,10 +9239,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>41313</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>41320</v>
       </c>
       <c r="C8" t="n">
@@ -9259,10 +9271,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>41390</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>41396</v>
       </c>
       <c r="C9" t="n">
@@ -9291,10 +9303,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>41474</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>41480</v>
       </c>
       <c r="C10" t="n">
@@ -9323,10 +9335,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>41547</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>41577</v>
       </c>
       <c r="C11" t="n">
@@ -9355,10 +9367,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>41669</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>41676</v>
       </c>
       <c r="C12" t="n">
@@ -9387,10 +9399,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>41746</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>41753</v>
       </c>
       <c r="C13" t="n">
@@ -9419,10 +9431,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>41837</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>41844</v>
       </c>
       <c r="C14" t="n">
@@ -9451,10 +9463,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>41928</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>41935</v>
       </c>
       <c r="C15" t="n">
@@ -9483,10 +9495,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>42032</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>42039</v>
       </c>
       <c r="C16" t="n">
@@ -9515,10 +9527,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>42110</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>42117</v>
       </c>
       <c r="C17" t="n">
@@ -9547,10 +9559,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>42201</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>42208</v>
       </c>
       <c r="C18" t="n">
@@ -9579,10 +9591,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>42291</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>42298</v>
       </c>
       <c r="C19" t="n">
@@ -9611,10 +9623,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>42396</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>42403</v>
       </c>
       <c r="C20" t="n">
@@ -9643,10 +9655,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>42474</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>42481</v>
       </c>
       <c r="C21" t="n">
@@ -9675,10 +9687,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>42565</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>42572</v>
       </c>
       <c r="C22" t="n">
@@ -9707,10 +9719,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>42661</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>42668</v>
       </c>
       <c r="C23" t="n">
@@ -9739,10 +9751,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>42766</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>42773</v>
       </c>
       <c r="C24" t="n">
@@ -9771,10 +9783,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>42846</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>42853</v>
       </c>
       <c r="C25" t="n">
@@ -9803,10 +9815,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>42933</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42941</v>
       </c>
       <c r="C26" t="n">
@@ -9835,10 +9847,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>43025</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>43032</v>
       </c>
       <c r="C27" t="n">
@@ -9867,10 +9879,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>43130</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>43137</v>
       </c>
       <c r="C28" t="n">
@@ -9899,10 +9911,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>43203</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>43216</v>
       </c>
       <c r="C29" t="n">
@@ -9931,10 +9943,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>43294</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>43306</v>
       </c>
       <c r="C30" t="n">
@@ -9963,10 +9975,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>43385</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="C31" t="n">
@@ -9995,10 +10007,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>43490</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>43502</v>
       </c>
       <c r="C32" t="n">
@@ -10027,10 +10039,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>43573</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="C33" t="n">
@@ -10059,10 +10071,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>43661</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>43678</v>
       </c>
       <c r="C34" t="n">
@@ -10091,10 +10103,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>43753</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>43767</v>
       </c>
       <c r="C35" t="n">
@@ -10123,10 +10135,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>43854</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>43866</v>
       </c>
       <c r="C36" t="n">
@@ -10155,10 +10167,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>43941</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43957</v>
       </c>
       <c r="C37" t="n">
@@ -10187,10 +10199,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>44027</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>44041</v>
       </c>
       <c r="C38" t="n">
@@ -10219,10 +10231,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>44123</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>44140</v>
       </c>
       <c r="C39" t="n">
@@ -10251,10 +10263,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>44225</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>44237</v>
       </c>
       <c r="C40" t="n">
@@ -10283,10 +10295,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>44305</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>44321</v>
       </c>
       <c r="C41" t="n">
@@ -10315,10 +10327,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>44396</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>44412</v>
       </c>
       <c r="C42" t="n">
@@ -10347,10 +10359,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>44481</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>44496</v>
       </c>
       <c r="C43" t="n">
@@ -10379,10 +10391,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>44579</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>44594</v>
       </c>
       <c r="C44" t="n">
@@ -10411,10 +10423,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>44664</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>44678</v>
       </c>
       <c r="C45" t="n">
@@ -10443,10 +10455,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>44755</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>44768</v>
       </c>
       <c r="C46" t="n">
@@ -10475,10 +10487,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>44846</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>44859</v>
       </c>
       <c r="C47" t="n">
@@ -10507,10 +10519,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>44943</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="C48" t="n">
@@ -10539,10 +10551,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>45030</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>45041</v>
       </c>
       <c r="C49" t="n">
@@ -10571,10 +10583,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>45120</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>45132</v>
       </c>
       <c r="C50" t="n">
@@ -10603,10 +10615,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>45211</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>45223</v>
       </c>
       <c r="C51" t="n">
@@ -10635,10 +10647,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>45307</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>45321</v>
       </c>
       <c r="C52" t="n">
@@ -10667,10 +10679,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>45394</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>45405</v>
       </c>
       <c r="C53" t="n">
@@ -10699,10 +10711,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>45485</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>45496</v>
       </c>
       <c r="C54" t="n">
@@ -10731,10 +10743,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>45576</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>45587</v>
       </c>
       <c r="C55" t="n">
@@ -10763,10 +10775,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>45673</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>45685</v>
       </c>
       <c r="C56" t="n">
@@ -10795,10 +10807,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>45762</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>45778</v>
       </c>
       <c r="C57" t="n">
@@ -10827,10 +10839,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>45849</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>45860</v>
       </c>
       <c r="C58" t="n">
@@ -10859,10 +10871,10 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>45940</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45951</v>
       </c>
       <c r="C59" t="n">
@@ -10891,10 +10903,10 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>46037</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>46049</v>
       </c>
       <c r="C60" t="n">
@@ -10923,10 +10935,10 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>46129</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>46140</v>
       </c>
       <c r="C61" t="n">
@@ -10955,10 +10967,10 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>46213</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>46224</v>
       </c>
       <c r="C62" t="n">
@@ -11005,12 +11017,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>campo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>valor</t>
         </is>
@@ -11081,7 +11093,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="8">

--- a/salidas/empresas/GM.xlsx
+++ b/salidas/empresas/GM.xlsx
@@ -498,7 +498,7 @@
         <v>40512</v>
       </c>
       <c r="B2" t="n">
-        <v>25.33570289611816</v>
+        <v>25.3357105255127</v>
       </c>
       <c r="C2" t="n">
         <v>34.20000076293945</v>
@@ -517,7 +517,7 @@
         <v>40543</v>
       </c>
       <c r="B3" t="n">
-        <v>27.30625152587891</v>
+        <v>27.30625534057617</v>
       </c>
       <c r="C3" t="n">
         <v>36.86000061035156</v>
@@ -536,7 +536,7 @@
         <v>40574</v>
       </c>
       <c r="B4" t="n">
-        <v>27.03216552734375</v>
+        <v>27.03216361999512</v>
       </c>
       <c r="C4" t="n">
         <v>36.4900016784668</v>
@@ -555,7 +555,7 @@
         <v>40602</v>
       </c>
       <c r="B5" t="n">
-        <v>24.83935737609863</v>
+        <v>24.83935928344727</v>
       </c>
       <c r="C5" t="n">
         <v>33.52999877929688</v>
@@ -574,7 +574,7 @@
         <v>40633</v>
       </c>
       <c r="B6" t="n">
-        <v>22.98733711242676</v>
+        <v>22.98733520507812</v>
       </c>
       <c r="C6" t="n">
         <v>31.03000068664551</v>
@@ -593,7 +593,7 @@
         <v>40663</v>
       </c>
       <c r="B7" t="n">
-        <v>23.77259063720703</v>
+        <v>23.7725887298584</v>
       </c>
       <c r="C7" t="n">
         <v>32.09000015258789</v>
@@ -612,7 +612,7 @@
         <v>40694</v>
       </c>
       <c r="B8" t="n">
-        <v>23.56516265869141</v>
+        <v>23.56516647338867</v>
       </c>
       <c r="C8" t="n">
         <v>31.80999946594238</v>
@@ -631,7 +631,7 @@
         <v>40724</v>
       </c>
       <c r="B9" t="n">
-        <v>22.49099731445312</v>
+        <v>22.49099540710449</v>
       </c>
       <c r="C9" t="n">
         <v>30.36000061035156</v>
@@ -669,7 +669,7 @@
         <v>40786</v>
       </c>
       <c r="B11" t="n">
-        <v>17.80166053771973</v>
+        <v>17.80166244506836</v>
       </c>
       <c r="C11" t="n">
         <v>24.03000068664551</v>
@@ -694,7 +694,7 @@
         <v>40816</v>
       </c>
       <c r="B12" t="n">
-        <v>14.94954872131348</v>
+        <v>14.94954204559326</v>
       </c>
       <c r="C12" t="n">
         <v>20.18000030517578</v>
@@ -744,7 +744,7 @@
         <v>40877</v>
       </c>
       <c r="B14" t="n">
-        <v>15.77184391021729</v>
+        <v>15.77184867858887</v>
       </c>
       <c r="C14" t="n">
         <v>21.29000091552734</v>
@@ -769,7 +769,7 @@
         <v>40908</v>
       </c>
       <c r="B15" t="n">
-        <v>15.01621723175049</v>
+        <v>15.01621913909912</v>
       </c>
       <c r="C15" t="n">
         <v>20.27000045776367</v>
@@ -794,7 +794,7 @@
         <v>40939</v>
       </c>
       <c r="B16" t="n">
-        <v>17.79425811767578</v>
+        <v>17.79425621032715</v>
       </c>
       <c r="C16" t="n">
         <v>24.02000045776367</v>
@@ -819,7 +819,7 @@
         <v>40968</v>
       </c>
       <c r="B17" t="n">
-        <v>19.27587890625</v>
+        <v>19.27588081359863</v>
       </c>
       <c r="C17" t="n">
         <v>26.02000045776367</v>
@@ -877,7 +877,7 @@
         <v>41029</v>
       </c>
       <c r="B19" t="n">
-        <v>17.03862571716309</v>
+        <v>17.03863334655762</v>
       </c>
       <c r="C19" t="n">
         <v>23</v>
@@ -906,7 +906,7 @@
         <v>41060</v>
       </c>
       <c r="B20" t="n">
-        <v>16.44598388671875</v>
+        <v>16.44598007202148</v>
       </c>
       <c r="C20" t="n">
         <v>22.20000076293945</v>
@@ -935,7 +935,7 @@
         <v>41090</v>
       </c>
       <c r="B21" t="n">
-        <v>14.60877323150635</v>
+        <v>14.60877704620361</v>
       </c>
       <c r="C21" t="n">
         <v>19.71999931335449</v>
@@ -964,7 +964,7 @@
         <v>41121</v>
       </c>
       <c r="B22" t="n">
-        <v>14.60136413574219</v>
+        <v>14.60136318206787</v>
       </c>
       <c r="C22" t="n">
         <v>19.70999908447266</v>
@@ -993,7 +993,7 @@
         <v>41152</v>
       </c>
       <c r="B23" t="n">
-        <v>15.8162956237793</v>
+        <v>15.81629085540771</v>
       </c>
       <c r="C23" t="n">
         <v>21.35000038146973</v>
@@ -1022,7 +1022,7 @@
         <v>41182</v>
       </c>
       <c r="B24" t="n">
-        <v>16.85342788696289</v>
+        <v>16.85342216491699</v>
       </c>
       <c r="C24" t="n">
         <v>22.75</v>
@@ -1076,7 +1076,7 @@
         <v>41243</v>
       </c>
       <c r="B26" t="n">
-        <v>19.17216300964355</v>
+        <v>19.17216491699219</v>
       </c>
       <c r="C26" t="n">
         <v>25.8799991607666</v>
@@ -1126,7 +1126,7 @@
         <v>41305</v>
       </c>
       <c r="B28" t="n">
-        <v>20.80934715270996</v>
+        <v>20.80935287475586</v>
       </c>
       <c r="C28" t="n">
         <v>28.09000015258789</v>
@@ -1151,7 +1151,7 @@
         <v>41333</v>
       </c>
       <c r="B29" t="n">
-        <v>20.11299324035645</v>
+        <v>20.11298942565918</v>
       </c>
       <c r="C29" t="n">
         <v>27.14999961853027</v>
@@ -1238,7 +1238,7 @@
         <v>41425</v>
       </c>
       <c r="B32" t="n">
-        <v>25.10604858398438</v>
+        <v>25.10605049133301</v>
       </c>
       <c r="C32" t="n">
         <v>33.88999938964844</v>
@@ -1267,7 +1267,7 @@
         <v>41455</v>
       </c>
       <c r="B33" t="n">
-        <v>24.6763801574707</v>
+        <v>24.6763858795166</v>
       </c>
       <c r="C33" t="n">
         <v>33.31000137329102</v>
@@ -1296,7 +1296,7 @@
         <v>41486</v>
       </c>
       <c r="B34" t="n">
-        <v>26.57285118103027</v>
+        <v>26.57285308837891</v>
       </c>
       <c r="C34" t="n">
         <v>35.86999893188477</v>
@@ -1325,7 +1325,7 @@
         <v>41517</v>
       </c>
       <c r="B35" t="n">
-        <v>25.24680709838867</v>
+        <v>25.2468090057373</v>
       </c>
       <c r="C35" t="n">
         <v>34.08000183105469</v>
@@ -1354,7 +1354,7 @@
         <v>41547</v>
       </c>
       <c r="B36" t="n">
-        <v>26.64694213867188</v>
+        <v>26.64694023132324</v>
       </c>
       <c r="C36" t="n">
         <v>35.97000122070312</v>
@@ -1379,7 +1379,7 @@
         <v>41578</v>
       </c>
       <c r="B37" t="n">
-        <v>27.3729305267334</v>
+        <v>27.37293243408203</v>
       </c>
       <c r="C37" t="n">
         <v>36.95000076293945</v>
@@ -1404,7 +1404,7 @@
         <v>41608</v>
       </c>
       <c r="B38" t="n">
-        <v>28.69156265258789</v>
+        <v>28.69157791137695</v>
       </c>
       <c r="C38" t="n">
         <v>38.72999954223633</v>
@@ -1429,7 +1429,7 @@
         <v>41639</v>
       </c>
       <c r="B39" t="n">
-        <v>30.27689933776855</v>
+        <v>30.27690505981445</v>
       </c>
       <c r="C39" t="n">
         <v>40.86999893188477</v>
@@ -1454,7 +1454,7 @@
         <v>41670</v>
       </c>
       <c r="B40" t="n">
-        <v>26.72843170166016</v>
+        <v>26.72842597961426</v>
       </c>
       <c r="C40" t="n">
         <v>36.08000183105469</v>
@@ -1479,7 +1479,7 @@
         <v>41698</v>
       </c>
       <c r="B41" t="n">
-        <v>26.81732940673828</v>
+        <v>26.81732559204102</v>
       </c>
       <c r="C41" t="n">
         <v>36.20000076293945</v>
@@ -1508,7 +1508,7 @@
         <v>41729</v>
       </c>
       <c r="B42" t="n">
-        <v>25.72507095336914</v>
+        <v>25.72506332397461</v>
       </c>
       <c r="C42" t="n">
         <v>34.41999816894531</v>
@@ -1537,7 +1537,7 @@
         <v>41759</v>
       </c>
       <c r="B43" t="n">
-        <v>25.76991271972656</v>
+        <v>25.7699031829834</v>
       </c>
       <c r="C43" t="n">
         <v>34.47999954223633</v>
@@ -1566,7 +1566,7 @@
         <v>41790</v>
       </c>
       <c r="B44" t="n">
-        <v>25.84465026855469</v>
+        <v>25.84464263916016</v>
       </c>
       <c r="C44" t="n">
         <v>34.58000183105469</v>
@@ -1624,7 +1624,7 @@
         <v>41851</v>
       </c>
       <c r="B46" t="n">
-        <v>25.48744773864746</v>
+        <v>25.48744964599609</v>
       </c>
       <c r="C46" t="n">
         <v>33.81999969482422</v>
@@ -1653,7 +1653,7 @@
         <v>41882</v>
       </c>
       <c r="B47" t="n">
-        <v>26.22599601745605</v>
+        <v>26.22599029541016</v>
       </c>
       <c r="C47" t="n">
         <v>34.79999923706055</v>
@@ -1740,7 +1740,7 @@
         <v>41973</v>
       </c>
       <c r="B50" t="n">
-        <v>25.41401290893555</v>
+        <v>25.41401481628418</v>
       </c>
       <c r="C50" t="n">
         <v>33.43000030517578</v>
@@ -1769,7 +1769,7 @@
         <v>42004</v>
       </c>
       <c r="B51" t="n">
-        <v>26.77587890625</v>
+        <v>26.77588081359863</v>
       </c>
       <c r="C51" t="n">
         <v>34.90999984741211</v>
@@ -1798,7 +1798,7 @@
         <v>42035</v>
       </c>
       <c r="B52" t="n">
-        <v>25.01945495605469</v>
+        <v>25.01945686340332</v>
       </c>
       <c r="C52" t="n">
         <v>32.61999893188477</v>
@@ -1827,7 +1827,7 @@
         <v>42063</v>
       </c>
       <c r="B53" t="n">
-        <v>28.61666870117188</v>
+        <v>28.61668395996094</v>
       </c>
       <c r="C53" t="n">
         <v>37.31000137329102</v>
@@ -1856,7 +1856,7 @@
         <v>42094</v>
       </c>
       <c r="B54" t="n">
-        <v>28.99855422973633</v>
+        <v>28.9985523223877</v>
       </c>
       <c r="C54" t="n">
         <v>37.5</v>
@@ -1885,7 +1885,7 @@
         <v>42124</v>
       </c>
       <c r="B55" t="n">
-        <v>27.1117057800293</v>
+        <v>27.11170959472656</v>
       </c>
       <c r="C55" t="n">
         <v>35.06000137329102</v>
@@ -1914,7 +1914,7 @@
         <v>42155</v>
       </c>
       <c r="B56" t="n">
-        <v>27.81540107727051</v>
+        <v>27.81541061401367</v>
       </c>
       <c r="C56" t="n">
         <v>35.97000122070312</v>
@@ -1943,7 +1943,7 @@
         <v>42185</v>
       </c>
       <c r="B57" t="n">
-        <v>26.04084014892578</v>
+        <v>26.04085159301758</v>
       </c>
       <c r="C57" t="n">
         <v>33.33000183105469</v>
@@ -1972,7 +1972,7 @@
         <v>42216</v>
       </c>
       <c r="B58" t="n">
-        <v>24.61886978149414</v>
+        <v>24.61886787414551</v>
       </c>
       <c r="C58" t="n">
         <v>31.51000022888184</v>
@@ -2030,7 +2030,7 @@
         <v>42277</v>
       </c>
       <c r="B60" t="n">
-        <v>23.74330139160156</v>
+        <v>23.74331092834473</v>
       </c>
       <c r="C60" t="n">
         <v>30.02000045776367</v>
@@ -2088,7 +2088,7 @@
         <v>42338</v>
       </c>
       <c r="B62" t="n">
-        <v>28.63117027282715</v>
+        <v>28.63116264343262</v>
       </c>
       <c r="C62" t="n">
         <v>36.20000076293945</v>
@@ -2117,7 +2117,7 @@
         <v>42369</v>
       </c>
       <c r="B63" t="n">
-        <v>27.18237113952637</v>
+        <v>27.182373046875</v>
       </c>
       <c r="C63" t="n">
         <v>34.0099983215332</v>
@@ -2146,7 +2146,7 @@
         <v>42400</v>
       </c>
       <c r="B64" t="n">
-        <v>23.68966865539551</v>
+        <v>23.68966674804688</v>
       </c>
       <c r="C64" t="n">
         <v>29.63999938964844</v>
@@ -2175,7 +2175,7 @@
         <v>42429</v>
       </c>
       <c r="B65" t="n">
-        <v>23.52981948852539</v>
+        <v>23.52981376647949</v>
       </c>
       <c r="C65" t="n">
         <v>29.44000053405762</v>
@@ -2204,7 +2204,7 @@
         <v>42460</v>
       </c>
       <c r="B66" t="n">
-        <v>25.43535423278809</v>
+        <v>25.43535995483398</v>
       </c>
       <c r="C66" t="n">
         <v>31.43000030517578</v>
@@ -2233,7 +2233,7 @@
         <v>42490</v>
       </c>
       <c r="B67" t="n">
-        <v>25.73478507995605</v>
+        <v>25.73479461669922</v>
       </c>
       <c r="C67" t="n">
         <v>31.79999923706055</v>
@@ -2262,7 +2262,7 @@
         <v>42521</v>
       </c>
       <c r="B68" t="n">
-        <v>25.3139705657959</v>
+        <v>25.31396675109863</v>
       </c>
       <c r="C68" t="n">
         <v>31.28000068664551</v>
@@ -2291,7 +2291,7 @@
         <v>42551</v>
       </c>
       <c r="B69" t="n">
-        <v>23.19389343261719</v>
+        <v>23.19389915466309</v>
       </c>
       <c r="C69" t="n">
         <v>28.29999923706055</v>
@@ -2320,7 +2320,7 @@
         <v>42582</v>
       </c>
       <c r="B70" t="n">
-        <v>25.84931373596191</v>
+        <v>25.84930610656738</v>
       </c>
       <c r="C70" t="n">
         <v>31.54000091552734</v>
@@ -2349,7 +2349,7 @@
         <v>42613</v>
       </c>
       <c r="B71" t="n">
-        <v>26.16074752807617</v>
+        <v>26.16074371337891</v>
       </c>
       <c r="C71" t="n">
         <v>31.92000007629395</v>
@@ -2436,7 +2436,7 @@
         <v>42704</v>
       </c>
       <c r="B74" t="n">
-        <v>28.63863754272461</v>
+        <v>28.63864707946777</v>
       </c>
       <c r="C74" t="n">
         <v>34.52999877929688</v>
@@ -2494,7 +2494,7 @@
         <v>42766</v>
       </c>
       <c r="B76" t="n">
-        <v>30.69314956665039</v>
+        <v>30.69314575195312</v>
       </c>
       <c r="C76" t="n">
         <v>36.61000061035156</v>
@@ -2523,7 +2523,7 @@
         <v>42794</v>
       </c>
       <c r="B77" t="n">
-        <v>30.8859748840332</v>
+        <v>30.88597106933594</v>
       </c>
       <c r="C77" t="n">
         <v>36.84000015258789</v>
@@ -2581,7 +2581,7 @@
         <v>42855</v>
       </c>
       <c r="B79" t="n">
-        <v>29.33866882324219</v>
+        <v>29.33867454528809</v>
       </c>
       <c r="C79" t="n">
         <v>34.63999938964844</v>
@@ -2668,7 +2668,7 @@
         <v>42947</v>
       </c>
       <c r="B82" t="n">
-        <v>30.81368255615234</v>
+        <v>30.81368827819824</v>
       </c>
       <c r="C82" t="n">
         <v>35.97999954223633</v>
@@ -2755,7 +2755,7 @@
         <v>43039</v>
       </c>
       <c r="B85" t="n">
-        <v>37.18365859985352</v>
+        <v>37.18365478515625</v>
       </c>
       <c r="C85" t="n">
         <v>42.97999954223633</v>
@@ -2784,7 +2784,7 @@
         <v>43069</v>
       </c>
       <c r="B86" t="n">
-        <v>37.27883148193359</v>
+        <v>37.27882766723633</v>
       </c>
       <c r="C86" t="n">
         <v>43.09000015258789</v>
@@ -2813,7 +2813,7 @@
         <v>43100</v>
       </c>
       <c r="B87" t="n">
-        <v>35.7846565246582</v>
+        <v>35.78464889526367</v>
       </c>
       <c r="C87" t="n">
         <v>40.9900016784668</v>
@@ -2842,7 +2842,7 @@
         <v>43131</v>
       </c>
       <c r="B88" t="n">
-        <v>37.02432250976562</v>
+        <v>37.02433013916016</v>
       </c>
       <c r="C88" t="n">
         <v>42.40999984741211</v>
@@ -2871,7 +2871,7 @@
         <v>43159</v>
       </c>
       <c r="B89" t="n">
-        <v>34.3529167175293</v>
+        <v>34.35290908813477</v>
       </c>
       <c r="C89" t="n">
         <v>39.34999847412109</v>
@@ -2898,7 +2898,7 @@
         <v>43190</v>
       </c>
       <c r="B90" t="n">
-        <v>32.0478401184082</v>
+        <v>32.04784393310547</v>
       </c>
       <c r="C90" t="n">
         <v>36.34000015258789</v>
@@ -2925,7 +2925,7 @@
         <v>43220</v>
       </c>
       <c r="B91" t="n">
-        <v>32.40059661865234</v>
+        <v>32.40060424804688</v>
       </c>
       <c r="C91" t="n">
         <v>36.7400016784668</v>
@@ -2952,7 +2952,7 @@
         <v>43251</v>
       </c>
       <c r="B92" t="n">
-        <v>37.65664291381836</v>
+        <v>37.65666198730469</v>
       </c>
       <c r="C92" t="n">
         <v>42.70000076293945</v>
@@ -3006,7 +3006,7 @@
         <v>43312</v>
       </c>
       <c r="B94" t="n">
-        <v>33.72412490844727</v>
+        <v>33.7241325378418</v>
       </c>
       <c r="C94" t="n">
         <v>37.90999984741211</v>
@@ -3033,7 +3033,7 @@
         <v>43343</v>
       </c>
       <c r="B95" t="n">
-        <v>32.06949615478516</v>
+        <v>32.06949234008789</v>
       </c>
       <c r="C95" t="n">
         <v>36.04999923706055</v>
@@ -3087,7 +3087,7 @@
         <v>43404</v>
       </c>
       <c r="B97" t="n">
-        <v>32.9041862487793</v>
+        <v>32.90419006347656</v>
       </c>
       <c r="C97" t="n">
         <v>36.59000015258789</v>
@@ -3116,7 +3116,7 @@
         <v>43434</v>
       </c>
       <c r="B98" t="n">
-        <v>34.12720108032227</v>
+        <v>34.127197265625</v>
       </c>
       <c r="C98" t="n">
         <v>37.95000076293945</v>
@@ -3232,7 +3232,7 @@
         <v>43555</v>
       </c>
       <c r="B102" t="n">
-        <v>34.04819869995117</v>
+        <v>34.04819488525391</v>
       </c>
       <c r="C102" t="n">
         <v>37.09999847412109</v>
@@ -3290,7 +3290,7 @@
         <v>43616</v>
       </c>
       <c r="B104" t="n">
-        <v>30.59748458862305</v>
+        <v>30.59748268127441</v>
       </c>
       <c r="C104" t="n">
         <v>33.34000015258789</v>
@@ -3348,7 +3348,7 @@
         <v>43677</v>
       </c>
       <c r="B106" t="n">
-        <v>37.41840744018555</v>
+        <v>37.41840362548828</v>
       </c>
       <c r="C106" t="n">
         <v>40.34000015258789</v>
@@ -3377,7 +3377,7 @@
         <v>43708</v>
       </c>
       <c r="B107" t="n">
-        <v>34.40378570556641</v>
+        <v>34.40378189086914</v>
       </c>
       <c r="C107" t="n">
         <v>37.09000015258789</v>
@@ -3406,7 +3406,7 @@
         <v>43738</v>
       </c>
       <c r="B108" t="n">
-        <v>35.11448287963867</v>
+        <v>35.11447906494141</v>
       </c>
       <c r="C108" t="n">
         <v>37.47999954223633</v>
@@ -3464,7 +3464,7 @@
         <v>43799</v>
       </c>
       <c r="B110" t="n">
-        <v>33.7278938293457</v>
+        <v>33.72788619995117</v>
       </c>
       <c r="C110" t="n">
         <v>36</v>
@@ -3522,7 +3522,7 @@
         <v>43861</v>
       </c>
       <c r="B112" t="n">
-        <v>31.61822700500488</v>
+        <v>31.61823081970215</v>
       </c>
       <c r="C112" t="n">
         <v>33.38999938964844</v>
@@ -3551,7 +3551,7 @@
         <v>43890</v>
       </c>
       <c r="B113" t="n">
-        <v>28.88158226013184</v>
+        <v>28.88158416748047</v>
       </c>
       <c r="C113" t="n">
         <v>30.5</v>
@@ -3580,7 +3580,7 @@
         <v>43921</v>
       </c>
       <c r="B114" t="n">
-        <v>19.91739654541016</v>
+        <v>19.91740036010742</v>
       </c>
       <c r="C114" t="n">
         <v>20.78000068664551</v>
@@ -3609,7 +3609,7 @@
         <v>43951</v>
       </c>
       <c r="B115" t="n">
-        <v>21.36471748352051</v>
+        <v>21.36472129821777</v>
       </c>
       <c r="C115" t="n">
         <v>22.29000091552734</v>
@@ -3667,7 +3667,7 @@
         <v>44012</v>
       </c>
       <c r="B117" t="n">
-        <v>24.24976539611816</v>
+        <v>24.24976921081543</v>
       </c>
       <c r="C117" t="n">
         <v>25.29999923706055</v>
@@ -3725,7 +3725,7 @@
         <v>44074</v>
       </c>
       <c r="B119" t="n">
-        <v>28.40002632141113</v>
+        <v>28.4000244140625</v>
       </c>
       <c r="C119" t="n">
         <v>29.6299991607666</v>
@@ -3754,7 +3754,7 @@
         <v>44104</v>
       </c>
       <c r="B120" t="n">
-        <v>28.36168670654297</v>
+        <v>28.3616886138916</v>
       </c>
       <c r="C120" t="n">
         <v>29.59000015258789</v>
@@ -3783,7 +3783,7 @@
         <v>44135</v>
       </c>
       <c r="B121" t="n">
-        <v>33.09661865234375</v>
+        <v>33.09661483764648</v>
       </c>
       <c r="C121" t="n">
         <v>34.52999877929688</v>
@@ -3841,7 +3841,7 @@
         <v>44196</v>
       </c>
       <c r="B123" t="n">
-        <v>39.91146469116211</v>
+        <v>39.91147613525391</v>
       </c>
       <c r="C123" t="n">
         <v>41.63999938964844</v>
@@ -3899,7 +3899,7 @@
         <v>44255</v>
       </c>
       <c r="B125" t="n">
-        <v>49.19923782348633</v>
+        <v>49.1992301940918</v>
       </c>
       <c r="C125" t="n">
         <v>51.33000183105469</v>
@@ -3928,7 +3928,7 @@
         <v>44286</v>
       </c>
       <c r="B126" t="n">
-        <v>55.07476806640625</v>
+        <v>55.07477569580078</v>
       </c>
       <c r="C126" t="n">
         <v>57.45999908447266</v>
@@ -3957,7 +3957,7 @@
         <v>44316</v>
       </c>
       <c r="B127" t="n">
-        <v>54.84473037719727</v>
+        <v>54.84473419189453</v>
       </c>
       <c r="C127" t="n">
         <v>57.22000122070312</v>
@@ -3986,7 +3986,7 @@
         <v>44347</v>
       </c>
       <c r="B128" t="n">
-        <v>56.84797286987305</v>
+        <v>56.84796905517578</v>
       </c>
       <c r="C128" t="n">
         <v>59.31000137329102</v>
@@ -4015,7 +4015,7 @@
         <v>44377</v>
       </c>
       <c r="B129" t="n">
-        <v>56.71378326416016</v>
+        <v>56.71377944946289</v>
       </c>
       <c r="C129" t="n">
         <v>59.16999816894531</v>
@@ -4044,7 +4044,7 @@
         <v>44408</v>
       </c>
       <c r="B130" t="n">
-        <v>54.48050689697266</v>
+        <v>54.48050308227539</v>
       </c>
       <c r="C130" t="n">
         <v>56.84000015258789</v>
@@ -4102,7 +4102,7 @@
         <v>44469</v>
       </c>
       <c r="B132" t="n">
-        <v>50.52195358276367</v>
+        <v>50.52194213867188</v>
       </c>
       <c r="C132" t="n">
         <v>52.70999908447266</v>
@@ -4131,7 +4131,7 @@
         <v>44500</v>
       </c>
       <c r="B133" t="n">
-        <v>52.17054748535156</v>
+        <v>52.17055130004883</v>
       </c>
       <c r="C133" t="n">
         <v>54.43000030517578</v>
@@ -4160,7 +4160,7 @@
         <v>44530</v>
       </c>
       <c r="B134" t="n">
-        <v>55.46774673461914</v>
+        <v>55.46775436401367</v>
       </c>
       <c r="C134" t="n">
         <v>57.86999893188477</v>
@@ -4218,7 +4218,7 @@
         <v>44592</v>
       </c>
       <c r="B136" t="n">
-        <v>50.54110717773438</v>
+        <v>50.54111099243164</v>
       </c>
       <c r="C136" t="n">
         <v>52.72999954223633</v>
@@ -4247,7 +4247,7 @@
         <v>44620</v>
       </c>
       <c r="B137" t="n">
-        <v>44.78060531616211</v>
+        <v>44.78059768676758</v>
       </c>
       <c r="C137" t="n">
         <v>46.72000122070312</v>
@@ -4276,7 +4276,7 @@
         <v>44651</v>
       </c>
       <c r="B138" t="n">
-        <v>41.92430114746094</v>
+        <v>41.9243049621582</v>
       </c>
       <c r="C138" t="n">
         <v>43.7400016784668</v>
@@ -4305,7 +4305,7 @@
         <v>44681</v>
       </c>
       <c r="B139" t="n">
-        <v>36.33631134033203</v>
+        <v>36.33630752563477</v>
       </c>
       <c r="C139" t="n">
         <v>37.90999984741211</v>
@@ -4334,7 +4334,7 @@
         <v>44712</v>
       </c>
       <c r="B140" t="n">
-        <v>37.07434463500977</v>
+        <v>37.07434844970703</v>
       </c>
       <c r="C140" t="n">
         <v>38.68000030517578</v>
@@ -4363,7 +4363,7 @@
         <v>44742</v>
       </c>
       <c r="B141" t="n">
-        <v>30.44160461425781</v>
+        <v>30.44160652160645</v>
       </c>
       <c r="C141" t="n">
         <v>31.76000022888184</v>
@@ -4450,7 +4450,7 @@
         <v>44834</v>
       </c>
       <c r="B144" t="n">
-        <v>30.82813453674316</v>
+        <v>30.82813262939453</v>
       </c>
       <c r="C144" t="n">
         <v>32.09000015258789</v>
@@ -4508,7 +4508,7 @@
         <v>44895</v>
       </c>
       <c r="B146" t="n">
-        <v>38.96506118774414</v>
+        <v>38.96507263183594</v>
       </c>
       <c r="C146" t="n">
         <v>40.56000137329102</v>
@@ -4566,7 +4566,7 @@
         <v>44957</v>
       </c>
       <c r="B148" t="n">
-        <v>37.85782623291016</v>
+        <v>37.85783004760742</v>
       </c>
       <c r="C148" t="n">
         <v>39.31999969482422</v>
@@ -4595,7 +4595,7 @@
         <v>44985</v>
       </c>
       <c r="B149" t="n">
-        <v>37.29940032958984</v>
+        <v>37.29940414428711</v>
       </c>
       <c r="C149" t="n">
         <v>38.7400016784668</v>
@@ -4682,7 +4682,7 @@
         <v>45077</v>
       </c>
       <c r="B152" t="n">
-        <v>31.27748870849609</v>
+        <v>31.27748680114746</v>
       </c>
       <c r="C152" t="n">
         <v>32.40999984741211</v>
@@ -4711,7 +4711,7 @@
         <v>45107</v>
       </c>
       <c r="B153" t="n">
-        <v>37.31621170043945</v>
+        <v>37.31621932983398</v>
       </c>
       <c r="C153" t="n">
         <v>38.56000137329102</v>
@@ -4740,7 +4740,7 @@
         <v>45138</v>
       </c>
       <c r="B154" t="n">
-        <v>37.13233947753906</v>
+        <v>37.13234329223633</v>
       </c>
       <c r="C154" t="n">
         <v>38.36999893188477</v>
@@ -4769,7 +4769,7 @@
         <v>45169</v>
       </c>
       <c r="B155" t="n">
-        <v>32.51675796508789</v>
+        <v>32.51675415039062</v>
       </c>
       <c r="C155" t="n">
         <v>33.5099983215332</v>
@@ -4798,7 +4798,7 @@
         <v>45199</v>
       </c>
       <c r="B156" t="n">
-        <v>31.99276161193848</v>
+        <v>31.99275779724121</v>
       </c>
       <c r="C156" t="n">
         <v>32.97000122070312</v>
@@ -4827,7 +4827,7 @@
         <v>45230</v>
       </c>
       <c r="B157" t="n">
-        <v>27.36414337158203</v>
+        <v>27.36414527893066</v>
       </c>
       <c r="C157" t="n">
         <v>28.20000076293945</v>
@@ -4856,7 +4856,7 @@
         <v>45260</v>
       </c>
       <c r="B158" t="n">
-        <v>30.75094795227051</v>
+        <v>30.75094604492188</v>
       </c>
       <c r="C158" t="n">
         <v>31.60000038146973</v>
@@ -4914,7 +4914,7 @@
         <v>45322</v>
       </c>
       <c r="B160" t="n">
-        <v>37.75749206542969</v>
+        <v>37.75748825073242</v>
       </c>
       <c r="C160" t="n">
         <v>38.79999923706055</v>
@@ -4972,7 +4972,7 @@
         <v>45382</v>
       </c>
       <c r="B162" t="n">
-        <v>44.26222991943359</v>
+        <v>44.26223373413086</v>
       </c>
       <c r="C162" t="n">
         <v>45.34999847412109</v>
@@ -5030,7 +5030,7 @@
         <v>45443</v>
       </c>
       <c r="B164" t="n">
-        <v>43.91086578369141</v>
+        <v>43.91086196899414</v>
       </c>
       <c r="C164" t="n">
         <v>44.9900016784668</v>
@@ -5059,7 +5059,7 @@
         <v>45473</v>
       </c>
       <c r="B165" t="n">
-        <v>45.46522903442383</v>
+        <v>45.4652214050293</v>
       </c>
       <c r="C165" t="n">
         <v>46.45999908447266</v>
@@ -5088,7 +5088,7 @@
         <v>45504</v>
       </c>
       <c r="B166" t="n">
-        <v>43.37104415893555</v>
+        <v>43.37104034423828</v>
       </c>
       <c r="C166" t="n">
         <v>44.31999969482422</v>
@@ -5146,7 +5146,7 @@
         <v>45565</v>
       </c>
       <c r="B168" t="n">
-        <v>43.98954010009766</v>
+        <v>43.98954391479492</v>
       </c>
       <c r="C168" t="n">
         <v>44.84000015258789</v>
@@ -5175,7 +5175,7 @@
         <v>45596</v>
       </c>
       <c r="B169" t="n">
-        <v>49.7972526550293</v>
+        <v>49.79726028442383</v>
       </c>
       <c r="C169" t="n">
         <v>50.7599983215332</v>
@@ -5233,7 +5233,7 @@
         <v>45657</v>
       </c>
       <c r="B171" t="n">
-        <v>52.37738037109375</v>
+        <v>52.37737655639648</v>
       </c>
       <c r="C171" t="n">
         <v>53.27000045776367</v>
@@ -5262,7 +5262,7 @@
         <v>45688</v>
       </c>
       <c r="B172" t="n">
-        <v>48.63121795654297</v>
+        <v>48.63122177124023</v>
       </c>
       <c r="C172" t="n">
         <v>49.45999908447266</v>
@@ -5291,7 +5291,7 @@
         <v>45716</v>
       </c>
       <c r="B173" t="n">
-        <v>48.30675506591797</v>
+        <v>48.3067512512207</v>
       </c>
       <c r="C173" t="n">
         <v>49.13000106811523</v>
@@ -5320,7 +5320,7 @@
         <v>45747</v>
       </c>
       <c r="B174" t="n">
-        <v>46.35980224609375</v>
+        <v>46.35980606079102</v>
       </c>
       <c r="C174" t="n">
         <v>47.02999877929688</v>
@@ -5349,7 +5349,7 @@
         <v>45777</v>
       </c>
       <c r="B175" t="n">
-        <v>44.59531021118164</v>
+        <v>44.59531402587891</v>
       </c>
       <c r="C175" t="n">
         <v>45.2400016784668</v>
@@ -5378,7 +5378,7 @@
         <v>45808</v>
       </c>
       <c r="B176" t="n">
-        <v>48.90303802490234</v>
+        <v>48.90304183959961</v>
       </c>
       <c r="C176" t="n">
         <v>49.61000061035156</v>
@@ -5523,7 +5523,7 @@
         <v>45961</v>
       </c>
       <c r="B181" t="n">
-        <v>68.49903106689453</v>
+        <v>68.4990234375</v>
       </c>
       <c r="C181" t="n">
         <v>69.08999633789062</v>
@@ -5639,7 +5639,7 @@
         <v>46081</v>
       </c>
       <c r="B185" t="n">
-        <v>78.19252014160156</v>
+        <v>78.19252777099609</v>
       </c>
       <c r="C185" t="n">
         <v>78.70999908447266</v>
@@ -5668,7 +5668,7 @@
         <v>46112</v>
       </c>
       <c r="B186" t="n">
-        <v>74.18544006347656</v>
+        <v>74.18544769287109</v>
       </c>
       <c r="C186" t="n">
         <v>74.5</v>
@@ -5726,7 +5726,7 @@
         <v>46173</v>
       </c>
       <c r="B188" t="n">
-        <v>82.88853454589844</v>
+        <v>82.88854217529297</v>
       </c>
       <c r="C188" t="n">
         <v>83.23999786376953</v>
